--- a/data_cache/excel/MARINE_historical.xlsx
+++ b/data_cache/excel/MARINE_historical.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E192"/>
+  <dimension ref="A1:G348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,15 +429,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>traded_quantity</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delivery_quantity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>delivery_pct</t>
         </is>
@@ -446,3630 +456,8676 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>240.85</v>
+        <v>232.72</v>
       </c>
       <c r="C2" t="n">
-        <v>496522</v>
+        <v>232.72</v>
       </c>
       <c r="D2" t="n">
-        <v>261677</v>
+        <v>232.72</v>
       </c>
       <c r="E2" t="n">
-        <v>52.7</v>
+        <v>500356</v>
+      </c>
+      <c r="F2" t="n">
+        <v>255797</v>
+      </c>
+      <c r="G2" t="n">
+        <v>51.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>245.7</v>
+        <v>230.19</v>
       </c>
       <c r="C3" t="n">
-        <v>1160210</v>
+        <v>230.19</v>
       </c>
       <c r="D3" t="n">
-        <v>390784</v>
+        <v>230.19</v>
       </c>
       <c r="E3" t="n">
-        <v>33.68</v>
+        <v>149364</v>
+      </c>
+      <c r="F3" t="n">
+        <v>96367</v>
+      </c>
+      <c r="G3" t="n">
+        <v>64.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>228.8</v>
+        <v>241.69</v>
       </c>
       <c r="C4" t="n">
-        <v>895722</v>
+        <v>241.69</v>
       </c>
       <c r="D4" t="n">
-        <v>520383</v>
+        <v>241.69</v>
       </c>
       <c r="E4" t="n">
-        <v>58.1</v>
+        <v>214262</v>
+      </c>
+      <c r="F4" t="n">
+        <v>180145</v>
+      </c>
+      <c r="G4" t="n">
+        <v>84.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>232.55</v>
+        <v>233.61</v>
       </c>
       <c r="C5" t="n">
-        <v>605195</v>
+        <v>233.61</v>
       </c>
       <c r="D5" t="n">
-        <v>247737</v>
+        <v>233.61</v>
       </c>
       <c r="E5" t="n">
-        <v>40.94</v>
+        <v>212067</v>
+      </c>
+      <c r="F5" t="n">
+        <v>140953</v>
+      </c>
+      <c r="G5" t="n">
+        <v>66.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2024-10-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>225.55</v>
+        <v>237.92</v>
       </c>
       <c r="C6" t="n">
-        <v>328490</v>
+        <v>237.92</v>
       </c>
       <c r="D6" t="n">
-        <v>171432</v>
+        <v>237.92</v>
       </c>
       <c r="E6" t="n">
-        <v>52.19</v>
+        <v>265196</v>
+      </c>
+      <c r="F6" t="n">
+        <v>159882</v>
+      </c>
+      <c r="G6" t="n">
+        <v>60.29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>237.2</v>
+        <v>236.26</v>
       </c>
       <c r="C7" t="n">
-        <v>560337</v>
+        <v>236.26</v>
       </c>
       <c r="D7" t="n">
-        <v>284264</v>
+        <v>236.26</v>
       </c>
       <c r="E7" t="n">
-        <v>50.73</v>
+        <v>189474</v>
+      </c>
+      <c r="F7" t="n">
+        <v>121579</v>
+      </c>
+      <c r="G7" t="n">
+        <v>64.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>238.1</v>
+        <v>230.84</v>
       </c>
       <c r="C8" t="n">
-        <v>546596</v>
+        <v>230.84</v>
       </c>
       <c r="D8" t="n">
-        <v>252002</v>
+        <v>230.84</v>
       </c>
       <c r="E8" t="n">
-        <v>46.1</v>
+        <v>188395</v>
+      </c>
+      <c r="F8" t="n">
+        <v>122554</v>
+      </c>
+      <c r="G8" t="n">
+        <v>65.05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>246.35</v>
+        <v>231.72</v>
       </c>
       <c r="C9" t="n">
-        <v>1642188</v>
+        <v>231.72</v>
       </c>
       <c r="D9" t="n">
-        <v>602486</v>
+        <v>231.72</v>
       </c>
       <c r="E9" t="n">
-        <v>36.69</v>
+        <v>114368</v>
+      </c>
+      <c r="F9" t="n">
+        <v>66126</v>
+      </c>
+      <c r="G9" t="n">
+        <v>57.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2024-10-18</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>250.2</v>
+        <v>233.09</v>
       </c>
       <c r="C10" t="n">
-        <v>601167</v>
+        <v>233.09</v>
       </c>
       <c r="D10" t="n">
-        <v>210362</v>
+        <v>233.09</v>
       </c>
       <c r="E10" t="n">
-        <v>34.99</v>
+        <v>232936</v>
+      </c>
+      <c r="F10" t="n">
+        <v>118826</v>
+      </c>
+      <c r="G10" t="n">
+        <v>51.01</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>247.35</v>
+        <v>221.61</v>
       </c>
       <c r="C11" t="n">
-        <v>367291</v>
+        <v>221.61</v>
       </c>
       <c r="D11" t="n">
-        <v>175436</v>
+        <v>221.61</v>
       </c>
       <c r="E11" t="n">
-        <v>47.76</v>
+        <v>219194</v>
+      </c>
+      <c r="F11" t="n">
+        <v>143907</v>
+      </c>
+      <c r="G11" t="n">
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>245.8</v>
+        <v>210.52</v>
       </c>
       <c r="C12" t="n">
-        <v>290105</v>
+        <v>210.52</v>
       </c>
       <c r="D12" t="n">
-        <v>138406</v>
+        <v>210.52</v>
       </c>
       <c r="E12" t="n">
-        <v>47.71</v>
+        <v>384429</v>
+      </c>
+      <c r="F12" t="n">
+        <v>268296</v>
+      </c>
+      <c r="G12" t="n">
+        <v>69.79000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>252.6</v>
+        <v>205.05</v>
       </c>
       <c r="C13" t="n">
-        <v>662379</v>
+        <v>205.05</v>
       </c>
       <c r="D13" t="n">
-        <v>277940</v>
+        <v>205.05</v>
       </c>
       <c r="E13" t="n">
-        <v>41.96</v>
+        <v>528623</v>
+      </c>
+      <c r="F13" t="n">
+        <v>326474</v>
+      </c>
+      <c r="G13" t="n">
+        <v>61.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2024-10-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>245.75</v>
+        <v>200.61</v>
       </c>
       <c r="C14" t="n">
-        <v>359959</v>
+        <v>200.61</v>
       </c>
       <c r="D14" t="n">
-        <v>144988</v>
+        <v>200.61</v>
       </c>
       <c r="E14" t="n">
-        <v>40.28</v>
+        <v>852133</v>
+      </c>
+      <c r="F14" t="n">
+        <v>441132</v>
+      </c>
+      <c r="G14" t="n">
+        <v>51.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>240.15</v>
+        <v>190.57</v>
       </c>
       <c r="C15" t="n">
-        <v>436058</v>
+        <v>190.57</v>
       </c>
       <c r="D15" t="n">
-        <v>184140</v>
+        <v>190.57</v>
       </c>
       <c r="E15" t="n">
-        <v>42.23</v>
+        <v>464705</v>
+      </c>
+      <c r="F15" t="n">
+        <v>352342</v>
+      </c>
+      <c r="G15" t="n">
+        <v>75.81999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2024-10-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>227.95</v>
+        <v>200.09</v>
       </c>
       <c r="C16" t="n">
-        <v>451228</v>
+        <v>200.09</v>
       </c>
       <c r="D16" t="n">
-        <v>235555</v>
+        <v>200.09</v>
       </c>
       <c r="E16" t="n">
-        <v>52.2</v>
+        <v>365314</v>
+      </c>
+      <c r="F16" t="n">
+        <v>175060</v>
+      </c>
+      <c r="G16" t="n">
+        <v>47.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>229.15</v>
+        <v>197.43</v>
       </c>
       <c r="C17" t="n">
-        <v>459443</v>
+        <v>197.43</v>
       </c>
       <c r="D17" t="n">
-        <v>147616</v>
+        <v>197.43</v>
       </c>
       <c r="E17" t="n">
-        <v>32.13</v>
+        <v>315178</v>
+      </c>
+      <c r="F17" t="n">
+        <v>172320</v>
+      </c>
+      <c r="G17" t="n">
+        <v>54.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>229.8</v>
+        <v>207.3</v>
       </c>
       <c r="C18" t="n">
-        <v>290799</v>
+        <v>207.3</v>
       </c>
       <c r="D18" t="n">
-        <v>94929</v>
+        <v>207.3</v>
       </c>
       <c r="E18" t="n">
-        <v>32.64</v>
+        <v>140242</v>
+      </c>
+      <c r="F18" t="n">
+        <v>89802</v>
+      </c>
+      <c r="G18" t="n">
+        <v>64.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>229.7</v>
+        <v>217.66</v>
       </c>
       <c r="C19" t="n">
-        <v>369715</v>
+        <v>217.66</v>
       </c>
       <c r="D19" t="n">
-        <v>134456</v>
+        <v>217.66</v>
       </c>
       <c r="E19" t="n">
-        <v>36.37</v>
+        <v>247563</v>
+      </c>
+      <c r="F19" t="n">
+        <v>133016</v>
+      </c>
+      <c r="G19" t="n">
+        <v>53.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>232.45</v>
+        <v>228.54</v>
       </c>
       <c r="C20" t="n">
-        <v>363084</v>
+        <v>228.54</v>
       </c>
       <c r="D20" t="n">
-        <v>142313</v>
+        <v>228.54</v>
       </c>
       <c r="E20" t="n">
-        <v>39.2</v>
+        <v>80715</v>
+      </c>
+      <c r="F20" t="n">
+        <v>80714</v>
+      </c>
+      <c r="G20" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>232.35</v>
+        <v>217.58</v>
       </c>
       <c r="C21" t="n">
-        <v>508587</v>
+        <v>217.58</v>
       </c>
       <c r="D21" t="n">
-        <v>186435</v>
+        <v>217.58</v>
       </c>
       <c r="E21" t="n">
-        <v>36.66</v>
+        <v>771023</v>
+      </c>
+      <c r="F21" t="n">
+        <v>376222</v>
+      </c>
+      <c r="G21" t="n">
+        <v>48.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>221.78</v>
+        <v>228.45</v>
       </c>
       <c r="C22" t="n">
-        <v>527277</v>
+        <v>228.45</v>
       </c>
       <c r="D22" t="n">
-        <v>289410</v>
+        <v>228.45</v>
       </c>
       <c r="E22" t="n">
-        <v>54.89</v>
+        <v>458783</v>
+      </c>
+      <c r="F22" t="n">
+        <v>240651</v>
+      </c>
+      <c r="G22" t="n">
+        <v>52.45</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>215.08</v>
+        <v>239.87</v>
       </c>
       <c r="C23" t="n">
-        <v>287055</v>
+        <v>239.87</v>
       </c>
       <c r="D23" t="n">
-        <v>154073</v>
+        <v>239.87</v>
       </c>
       <c r="E23" t="n">
-        <v>53.67</v>
+        <v>570311</v>
+      </c>
+      <c r="F23" t="n">
+        <v>356242</v>
+      </c>
+      <c r="G23" t="n">
+        <v>62.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>211.41</v>
+        <v>234.07</v>
       </c>
       <c r="C24" t="n">
-        <v>306356</v>
+        <v>234.07</v>
       </c>
       <c r="D24" t="n">
-        <v>162763</v>
+        <v>234.07</v>
       </c>
       <c r="E24" t="n">
-        <v>53.13</v>
+        <v>585142</v>
+      </c>
+      <c r="F24" t="n">
+        <v>300074</v>
+      </c>
+      <c r="G24" t="n">
+        <v>51.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-11-08</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>207.12</v>
+        <v>229.74</v>
       </c>
       <c r="C25" t="n">
-        <v>216556</v>
+        <v>229.74</v>
       </c>
       <c r="D25" t="n">
-        <v>105994</v>
+        <v>229.74</v>
       </c>
       <c r="E25" t="n">
-        <v>48.95</v>
+        <v>213732</v>
+      </c>
+      <c r="F25" t="n">
+        <v>122159</v>
+      </c>
+      <c r="G25" t="n">
+        <v>57.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2024-11-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>200.06</v>
+        <v>226.36</v>
       </c>
       <c r="C26" t="n">
-        <v>306661</v>
+        <v>226.36</v>
       </c>
       <c r="D26" t="n">
-        <v>172316</v>
+        <v>226.36</v>
       </c>
       <c r="E26" t="n">
-        <v>56.19</v>
+        <v>201114</v>
+      </c>
+      <c r="F26" t="n">
+        <v>92652</v>
+      </c>
+      <c r="G26" t="n">
+        <v>46.07</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>205.41</v>
+        <v>226.51</v>
       </c>
       <c r="C27" t="n">
-        <v>457952</v>
+        <v>226.51</v>
       </c>
       <c r="D27" t="n">
-        <v>185687</v>
+        <v>226.51</v>
       </c>
       <c r="E27" t="n">
-        <v>40.55</v>
+        <v>353027</v>
+      </c>
+      <c r="F27" t="n">
+        <v>155794</v>
+      </c>
+      <c r="G27" t="n">
+        <v>44.13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2024-11-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>201.55</v>
+        <v>223.95</v>
       </c>
       <c r="C28" t="n">
-        <v>227895</v>
+        <v>223.95</v>
       </c>
       <c r="D28" t="n">
-        <v>116405</v>
+        <v>223.95</v>
       </c>
       <c r="E28" t="n">
-        <v>51.08</v>
+        <v>786606</v>
+      </c>
+      <c r="F28" t="n">
+        <v>366518</v>
+      </c>
+      <c r="G28" t="n">
+        <v>46.59</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>203.44</v>
+        <v>226.41</v>
       </c>
       <c r="C29" t="n">
-        <v>194751</v>
+        <v>226.41</v>
       </c>
       <c r="D29" t="n">
-        <v>71867</v>
+        <v>226.41</v>
       </c>
       <c r="E29" t="n">
-        <v>36.9</v>
+        <v>511797</v>
+      </c>
+      <c r="F29" t="n">
+        <v>197315</v>
+      </c>
+      <c r="G29" t="n">
+        <v>38.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-11-15</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>202.89</v>
+        <v>226.41</v>
       </c>
       <c r="C30" t="n">
-        <v>234838</v>
+        <v>226.41</v>
       </c>
       <c r="D30" t="n">
-        <v>111687</v>
+        <v>226.41</v>
       </c>
       <c r="E30" t="n">
-        <v>47.56</v>
+        <v>511797</v>
+      </c>
+      <c r="F30" t="n">
+        <v>197315</v>
+      </c>
+      <c r="G30" t="n">
+        <v>38.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>204.21</v>
+        <v>218.42</v>
       </c>
       <c r="C31" t="n">
-        <v>138660</v>
+        <v>218.42</v>
       </c>
       <c r="D31" t="n">
-        <v>67811</v>
+        <v>218.42</v>
       </c>
       <c r="E31" t="n">
-        <v>48.9</v>
+        <v>284186</v>
+      </c>
+      <c r="F31" t="n">
+        <v>142261</v>
+      </c>
+      <c r="G31" t="n">
+        <v>50.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>204.02</v>
+        <v>227.81</v>
       </c>
       <c r="C32" t="n">
-        <v>169974</v>
+        <v>227.81</v>
       </c>
       <c r="D32" t="n">
-        <v>87983</v>
+        <v>227.81</v>
       </c>
       <c r="E32" t="n">
-        <v>51.76</v>
+        <v>450602</v>
+      </c>
+      <c r="F32" t="n">
+        <v>203109</v>
+      </c>
+      <c r="G32" t="n">
+        <v>45.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>202.95</v>
+        <v>227.81</v>
       </c>
       <c r="C33" t="n">
-        <v>152367</v>
+        <v>227.81</v>
       </c>
       <c r="D33" t="n">
-        <v>97613</v>
+        <v>227.81</v>
       </c>
       <c r="E33" t="n">
-        <v>64.06</v>
+        <v>450602</v>
+      </c>
+      <c r="F33" t="n">
+        <v>203109</v>
+      </c>
+      <c r="G33" t="n">
+        <v>45.08</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>200.49</v>
+        <v>224.54</v>
       </c>
       <c r="C34" t="n">
-        <v>162147</v>
+        <v>224.54</v>
       </c>
       <c r="D34" t="n">
-        <v>87459</v>
+        <v>224.54</v>
       </c>
       <c r="E34" t="n">
-        <v>53.94</v>
+        <v>299945</v>
+      </c>
+      <c r="F34" t="n">
+        <v>137252</v>
+      </c>
+      <c r="G34" t="n">
+        <v>45.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>202.89</v>
+        <v>225.07</v>
       </c>
       <c r="C35" t="n">
-        <v>138621</v>
+        <v>225.07</v>
       </c>
       <c r="D35" t="n">
-        <v>77492</v>
+        <v>225.07</v>
       </c>
       <c r="E35" t="n">
-        <v>55.9</v>
+        <v>152338</v>
+      </c>
+      <c r="F35" t="n">
+        <v>92432</v>
+      </c>
+      <c r="G35" t="n">
+        <v>60.68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>216.23</v>
+        <v>229.76</v>
       </c>
       <c r="C36" t="n">
-        <v>590436</v>
+        <v>229.76</v>
       </c>
       <c r="D36" t="n">
-        <v>231348</v>
+        <v>229.76</v>
       </c>
       <c r="E36" t="n">
-        <v>39.18</v>
+        <v>542399</v>
+      </c>
+      <c r="F36" t="n">
+        <v>203944</v>
+      </c>
+      <c r="G36" t="n">
+        <v>37.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2024-11-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>213.31</v>
+        <v>241.24</v>
       </c>
       <c r="C37" t="n">
-        <v>374031</v>
+        <v>241.24</v>
       </c>
       <c r="D37" t="n">
-        <v>112426</v>
+        <v>241.24</v>
       </c>
       <c r="E37" t="n">
-        <v>30.06</v>
+        <v>1265606</v>
+      </c>
+      <c r="F37" t="n">
+        <v>402700</v>
+      </c>
+      <c r="G37" t="n">
+        <v>31.82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>211.24</v>
+        <v>253.3</v>
       </c>
       <c r="C38" t="n">
-        <v>217216</v>
+        <v>253.3</v>
       </c>
       <c r="D38" t="n">
-        <v>79905</v>
+        <v>253.3</v>
       </c>
       <c r="E38" t="n">
-        <v>36.79</v>
+        <v>391305</v>
+      </c>
+      <c r="F38" t="n">
+        <v>281212</v>
+      </c>
+      <c r="G38" t="n">
+        <v>71.87</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>216.24</v>
+        <v>264.8</v>
       </c>
       <c r="C39" t="n">
-        <v>253191</v>
+        <v>264.8</v>
       </c>
       <c r="D39" t="n">
-        <v>117694</v>
+        <v>264.8</v>
       </c>
       <c r="E39" t="n">
-        <v>46.48</v>
+        <v>1430286</v>
+      </c>
+      <c r="F39" t="n">
+        <v>729123</v>
+      </c>
+      <c r="G39" t="n">
+        <v>50.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>210.15</v>
+        <v>262.09</v>
       </c>
       <c r="C40" t="n">
-        <v>211126</v>
+        <v>262.09</v>
       </c>
       <c r="D40" t="n">
-        <v>110853</v>
+        <v>262.09</v>
       </c>
       <c r="E40" t="n">
-        <v>52.51</v>
+        <v>692842</v>
+      </c>
+      <c r="F40" t="n">
+        <v>354872</v>
+      </c>
+      <c r="G40" t="n">
+        <v>51.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>211.98</v>
+        <v>265.35</v>
       </c>
       <c r="C41" t="n">
-        <v>195490</v>
+        <v>265.35</v>
       </c>
       <c r="D41" t="n">
-        <v>74339</v>
+        <v>265.35</v>
       </c>
       <c r="E41" t="n">
-        <v>38.03</v>
+        <v>513908</v>
+      </c>
+      <c r="F41" t="n">
+        <v>263910</v>
+      </c>
+      <c r="G41" t="n">
+        <v>51.35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-12-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>216.29</v>
+        <v>258.5</v>
       </c>
       <c r="C42" t="n">
-        <v>354659</v>
+        <v>258.5</v>
       </c>
       <c r="D42" t="n">
-        <v>144923</v>
+        <v>258.5</v>
       </c>
       <c r="E42" t="n">
-        <v>40.86</v>
+        <v>336462</v>
+      </c>
+      <c r="F42" t="n">
+        <v>198816</v>
+      </c>
+      <c r="G42" t="n">
+        <v>59.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2024-12-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>211.67</v>
+        <v>270.8</v>
       </c>
       <c r="C43" t="n">
-        <v>101318</v>
+        <v>270.8</v>
       </c>
       <c r="D43" t="n">
-        <v>59304</v>
+        <v>270.8</v>
       </c>
       <c r="E43" t="n">
-        <v>58.53</v>
+        <v>981312</v>
+      </c>
+      <c r="F43" t="n">
+        <v>509909</v>
+      </c>
+      <c r="G43" t="n">
+        <v>51.96</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>213.63</v>
+        <v>264.65</v>
       </c>
       <c r="C44" t="n">
-        <v>120850</v>
+        <v>264.65</v>
       </c>
       <c r="D44" t="n">
-        <v>60627</v>
+        <v>264.65</v>
       </c>
       <c r="E44" t="n">
-        <v>50.17</v>
+        <v>554513</v>
+      </c>
+      <c r="F44" t="n">
+        <v>275572</v>
+      </c>
+      <c r="G44" t="n">
+        <v>49.7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>217.66</v>
+        <v>276.2</v>
       </c>
       <c r="C45" t="n">
-        <v>601320</v>
+        <v>276.2</v>
       </c>
       <c r="D45" t="n">
-        <v>203402</v>
+        <v>276.2</v>
       </c>
       <c r="E45" t="n">
-        <v>33.83</v>
+        <v>1430496</v>
+      </c>
+      <c r="F45" t="n">
+        <v>633492</v>
+      </c>
+      <c r="G45" t="n">
+        <v>44.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>212.43</v>
+        <v>303.75</v>
       </c>
       <c r="C46" t="n">
-        <v>199360</v>
+        <v>303.75</v>
       </c>
       <c r="D46" t="n">
-        <v>109589</v>
+        <v>303.75</v>
       </c>
       <c r="E46" t="n">
-        <v>54.97</v>
+        <v>3840020</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1522335</v>
+      </c>
+      <c r="G46" t="n">
+        <v>39.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>214.21</v>
+        <v>300.65</v>
       </c>
       <c r="C47" t="n">
-        <v>157933</v>
+        <v>300.65</v>
       </c>
       <c r="D47" t="n">
-        <v>67599</v>
+        <v>300.65</v>
       </c>
       <c r="E47" t="n">
-        <v>42.8</v>
+        <v>1359282</v>
+      </c>
+      <c r="F47" t="n">
+        <v>643715</v>
+      </c>
+      <c r="G47" t="n">
+        <v>47.36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>210.67</v>
+        <v>298.7</v>
       </c>
       <c r="C48" t="n">
-        <v>241715</v>
+        <v>298.7</v>
       </c>
       <c r="D48" t="n">
-        <v>126806</v>
+        <v>298.7</v>
       </c>
       <c r="E48" t="n">
-        <v>52.46</v>
+        <v>626796</v>
+      </c>
+      <c r="F48" t="n">
+        <v>334112</v>
+      </c>
+      <c r="G48" t="n">
+        <v>53.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>203.3</v>
+        <v>303.15</v>
       </c>
       <c r="C49" t="n">
-        <v>287667</v>
+        <v>303.15</v>
       </c>
       <c r="D49" t="n">
-        <v>115895</v>
+        <v>303.15</v>
       </c>
       <c r="E49" t="n">
-        <v>40.29</v>
+        <v>1260504</v>
+      </c>
+      <c r="F49" t="n">
+        <v>562866</v>
+      </c>
+      <c r="G49" t="n">
+        <v>44.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>195.89</v>
+        <v>301.95</v>
       </c>
       <c r="C50" t="n">
-        <v>435697</v>
+        <v>301.95</v>
       </c>
       <c r="D50" t="n">
-        <v>191577</v>
+        <v>301.95</v>
       </c>
       <c r="E50" t="n">
-        <v>43.97</v>
+        <v>973600</v>
+      </c>
+      <c r="F50" t="n">
+        <v>401948</v>
+      </c>
+      <c r="G50" t="n">
+        <v>41.28</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>195.87</v>
+        <v>302.75</v>
       </c>
       <c r="C51" t="n">
-        <v>187258</v>
+        <v>302.75</v>
       </c>
       <c r="D51" t="n">
-        <v>89615</v>
+        <v>302.75</v>
       </c>
       <c r="E51" t="n">
-        <v>47.86</v>
+        <v>674217</v>
+      </c>
+      <c r="F51" t="n">
+        <v>311233</v>
+      </c>
+      <c r="G51" t="n">
+        <v>46.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>194.23</v>
+        <v>327.6</v>
       </c>
       <c r="C52" t="n">
-        <v>182447</v>
+        <v>327.6</v>
       </c>
       <c r="D52" t="n">
-        <v>95261</v>
+        <v>327.6</v>
       </c>
       <c r="E52" t="n">
-        <v>52.21</v>
+        <v>2483075</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1054102</v>
+      </c>
+      <c r="G52" t="n">
+        <v>42.45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>194.23</v>
+        <v>308.6</v>
       </c>
       <c r="C53" t="n">
-        <v>182447</v>
+        <v>308.6</v>
       </c>
       <c r="D53" t="n">
-        <v>95261</v>
+        <v>308.6</v>
       </c>
       <c r="E53" t="n">
-        <v>52.21</v>
+        <v>1138956</v>
+      </c>
+      <c r="F53" t="n">
+        <v>543277</v>
+      </c>
+      <c r="G53" t="n">
+        <v>47.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>191.67</v>
+        <v>309.3</v>
       </c>
       <c r="C54" t="n">
-        <v>235150</v>
+        <v>309.3</v>
       </c>
       <c r="D54" t="n">
-        <v>129777</v>
+        <v>309.3</v>
       </c>
       <c r="E54" t="n">
-        <v>55.19</v>
+        <v>1777827</v>
+      </c>
+      <c r="F54" t="n">
+        <v>492269</v>
+      </c>
+      <c r="G54" t="n">
+        <v>27.69</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>185.2</v>
+        <v>297.95</v>
       </c>
       <c r="C55" t="n">
-        <v>320191</v>
+        <v>297.95</v>
       </c>
       <c r="D55" t="n">
-        <v>173126</v>
+        <v>297.95</v>
       </c>
       <c r="E55" t="n">
-        <v>54.07</v>
+        <v>1073430</v>
+      </c>
+      <c r="F55" t="n">
+        <v>428659</v>
+      </c>
+      <c r="G55" t="n">
+        <v>39.93</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>176.14</v>
+        <v>289.85</v>
       </c>
       <c r="C56" t="n">
-        <v>507048</v>
+        <v>289.85</v>
       </c>
       <c r="D56" t="n">
-        <v>245388</v>
+        <v>289.85</v>
       </c>
       <c r="E56" t="n">
-        <v>48.4</v>
+        <v>778304</v>
+      </c>
+      <c r="F56" t="n">
+        <v>334908</v>
+      </c>
+      <c r="G56" t="n">
+        <v>43.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>175.96</v>
+        <v>289.1</v>
       </c>
       <c r="C57" t="n">
-        <v>287999</v>
+        <v>289.1</v>
       </c>
       <c r="D57" t="n">
-        <v>110660</v>
+        <v>289.1</v>
       </c>
       <c r="E57" t="n">
-        <v>38.42</v>
+        <v>420500</v>
+      </c>
+      <c r="F57" t="n">
+        <v>148026</v>
+      </c>
+      <c r="G57" t="n">
+        <v>35.2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2024-12-25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>182.18</v>
+        <v>289.1</v>
       </c>
       <c r="C58" t="n">
-        <v>181860</v>
+        <v>289.1</v>
       </c>
       <c r="D58" t="n">
-        <v>78358</v>
+        <v>289.1</v>
       </c>
       <c r="E58" t="n">
-        <v>43.09</v>
+        <v>420500</v>
+      </c>
+      <c r="F58" t="n">
+        <v>148026</v>
+      </c>
+      <c r="G58" t="n">
+        <v>35.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>170.49</v>
+        <v>276.4</v>
       </c>
       <c r="C59" t="n">
-        <v>457811</v>
+        <v>276.4</v>
       </c>
       <c r="D59" t="n">
-        <v>249785</v>
+        <v>276.4</v>
       </c>
       <c r="E59" t="n">
-        <v>54.56</v>
+        <v>752014</v>
+      </c>
+      <c r="F59" t="n">
+        <v>437913</v>
+      </c>
+      <c r="G59" t="n">
+        <v>58.23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>182.28</v>
+        <v>269.45</v>
       </c>
       <c r="C60" t="n">
-        <v>891603</v>
+        <v>269.45</v>
       </c>
       <c r="D60" t="n">
-        <v>272563</v>
+        <v>269.45</v>
       </c>
       <c r="E60" t="n">
-        <v>30.57</v>
+        <v>760625</v>
+      </c>
+      <c r="F60" t="n">
+        <v>358140</v>
+      </c>
+      <c r="G60" t="n">
+        <v>47.08</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>180</v>
+        <v>263.45</v>
       </c>
       <c r="C61" t="n">
-        <v>462390</v>
+        <v>263.45</v>
       </c>
       <c r="D61" t="n">
-        <v>214096</v>
+        <v>263.45</v>
       </c>
       <c r="E61" t="n">
-        <v>46.3</v>
+        <v>504181</v>
+      </c>
+      <c r="F61" t="n">
+        <v>210361</v>
+      </c>
+      <c r="G61" t="n">
+        <v>41.72</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>176.53</v>
+        <v>170.54</v>
       </c>
       <c r="C62" t="n">
-        <v>360152</v>
+        <v>170.54</v>
       </c>
       <c r="D62" t="n">
-        <v>183516</v>
+        <v>170.54</v>
       </c>
       <c r="E62" t="n">
-        <v>50.96</v>
+        <v>218642</v>
+      </c>
+      <c r="F62" t="n">
+        <v>175853</v>
+      </c>
+      <c r="G62" t="n">
+        <v>80.43000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>180.41</v>
+        <v>162.03</v>
       </c>
       <c r="C63" t="n">
-        <v>384145</v>
+        <v>162.03</v>
       </c>
       <c r="D63" t="n">
-        <v>177674</v>
+        <v>162.03</v>
       </c>
       <c r="E63" t="n">
-        <v>46.25</v>
+        <v>307710</v>
+      </c>
+      <c r="F63" t="n">
+        <v>201913</v>
+      </c>
+      <c r="G63" t="n">
+        <v>65.62</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>186.37</v>
+        <v>160.3</v>
       </c>
       <c r="C64" t="n">
-        <v>439529</v>
+        <v>160.3</v>
       </c>
       <c r="D64" t="n">
-        <v>151394</v>
+        <v>160.3</v>
       </c>
       <c r="E64" t="n">
-        <v>34.44</v>
+        <v>542262</v>
+      </c>
+      <c r="F64" t="n">
+        <v>325388</v>
+      </c>
+      <c r="G64" t="n">
+        <v>60.01</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>194.24</v>
+        <v>156.99</v>
       </c>
       <c r="C65" t="n">
-        <v>519678</v>
+        <v>156.99</v>
       </c>
       <c r="D65" t="n">
-        <v>255199</v>
+        <v>156.99</v>
       </c>
       <c r="E65" t="n">
-        <v>49.11</v>
+        <v>383443</v>
+      </c>
+      <c r="F65" t="n">
+        <v>228665</v>
+      </c>
+      <c r="G65" t="n">
+        <v>59.63</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>194.59</v>
+        <v>164.83</v>
       </c>
       <c r="C66" t="n">
-        <v>298628</v>
+        <v>164.83</v>
       </c>
       <c r="D66" t="n">
-        <v>152194</v>
+        <v>164.83</v>
       </c>
       <c r="E66" t="n">
-        <v>50.96</v>
+        <v>216311</v>
+      </c>
+      <c r="F66" t="n">
+        <v>104420</v>
+      </c>
+      <c r="G66" t="n">
+        <v>48.27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>190.91</v>
+        <v>173.07</v>
       </c>
       <c r="C67" t="n">
-        <v>157063</v>
+        <v>173.07</v>
       </c>
       <c r="D67" t="n">
-        <v>77781</v>
+        <v>173.07</v>
       </c>
       <c r="E67" t="n">
-        <v>49.52</v>
+        <v>551241</v>
+      </c>
+      <c r="F67" t="n">
+        <v>243456</v>
+      </c>
+      <c r="G67" t="n">
+        <v>44.17</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>188.14</v>
+        <v>181.49</v>
       </c>
       <c r="C68" t="n">
-        <v>151984</v>
+        <v>181.49</v>
       </c>
       <c r="D68" t="n">
-        <v>66045</v>
+        <v>181.49</v>
       </c>
       <c r="E68" t="n">
-        <v>43.46</v>
+        <v>605763</v>
+      </c>
+      <c r="F68" t="n">
+        <v>251475</v>
+      </c>
+      <c r="G68" t="n">
+        <v>41.51</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>198.57</v>
+        <v>172.61</v>
       </c>
       <c r="C69" t="n">
-        <v>483315</v>
+        <v>172.61</v>
       </c>
       <c r="D69" t="n">
-        <v>247905</v>
+        <v>172.61</v>
       </c>
       <c r="E69" t="n">
-        <v>51.29</v>
+        <v>517463</v>
+      </c>
+      <c r="F69" t="n">
+        <v>286515</v>
+      </c>
+      <c r="G69" t="n">
+        <v>55.37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>195.53</v>
+        <v>163.31</v>
       </c>
       <c r="C70" t="n">
-        <v>170928</v>
+        <v>163.31</v>
       </c>
       <c r="D70" t="n">
-        <v>97199</v>
+        <v>163.31</v>
       </c>
       <c r="E70" t="n">
-        <v>56.87</v>
+        <v>454056</v>
+      </c>
+      <c r="F70" t="n">
+        <v>232441</v>
+      </c>
+      <c r="G70" t="n">
+        <v>51.19</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>194.6</v>
+        <v>172.29</v>
       </c>
       <c r="C71" t="n">
-        <v>168385</v>
+        <v>172.29</v>
       </c>
       <c r="D71" t="n">
-        <v>94448</v>
+        <v>172.29</v>
       </c>
       <c r="E71" t="n">
-        <v>56.09</v>
+        <v>226390</v>
+      </c>
+      <c r="F71" t="n">
+        <v>96575</v>
+      </c>
+      <c r="G71" t="n">
+        <v>42.66</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>188.21</v>
+        <v>169.36</v>
       </c>
       <c r="C72" t="n">
-        <v>324228</v>
+        <v>169.36</v>
       </c>
       <c r="D72" t="n">
-        <v>146124</v>
+        <v>169.36</v>
       </c>
       <c r="E72" t="n">
-        <v>45.07</v>
+        <v>211540</v>
+      </c>
+      <c r="F72" t="n">
+        <v>88923</v>
+      </c>
+      <c r="G72" t="n">
+        <v>42.04</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>182.71</v>
+        <v>172.84</v>
       </c>
       <c r="C73" t="n">
-        <v>226167</v>
+        <v>172.84</v>
       </c>
       <c r="D73" t="n">
-        <v>99250</v>
+        <v>172.84</v>
       </c>
       <c r="E73" t="n">
-        <v>43.88</v>
+        <v>201879</v>
+      </c>
+      <c r="F73" t="n">
+        <v>87753</v>
+      </c>
+      <c r="G73" t="n">
+        <v>43.47</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>186.93</v>
+        <v>186.5</v>
       </c>
       <c r="C74" t="n">
-        <v>370128</v>
+        <v>186.5</v>
       </c>
       <c r="D74" t="n">
-        <v>130334</v>
+        <v>186.5</v>
       </c>
       <c r="E74" t="n">
-        <v>35.21</v>
+        <v>475545</v>
+      </c>
+      <c r="F74" t="n">
+        <v>229124</v>
+      </c>
+      <c r="G74" t="n">
+        <v>48.18</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>191.2</v>
+        <v>204.1</v>
       </c>
       <c r="C75" t="n">
-        <v>494120</v>
+        <v>204.1</v>
       </c>
       <c r="D75" t="n">
-        <v>139895</v>
+        <v>204.1</v>
       </c>
       <c r="E75" t="n">
-        <v>28.31</v>
+        <v>1221639</v>
+      </c>
+      <c r="F75" t="n">
+        <v>457508</v>
+      </c>
+      <c r="G75" t="n">
+        <v>37.45</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>195.25</v>
+        <v>203.34</v>
       </c>
       <c r="C76" t="n">
-        <v>392784</v>
+        <v>203.34</v>
       </c>
       <c r="D76" t="n">
-        <v>135586</v>
+        <v>203.34</v>
       </c>
       <c r="E76" t="n">
-        <v>34.52</v>
+        <v>992455</v>
+      </c>
+      <c r="F76" t="n">
+        <v>310686</v>
+      </c>
+      <c r="G76" t="n">
+        <v>31.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>188.84</v>
+        <v>208.66</v>
       </c>
       <c r="C77" t="n">
-        <v>203739</v>
+        <v>208.66</v>
       </c>
       <c r="D77" t="n">
-        <v>106485</v>
+        <v>208.66</v>
       </c>
       <c r="E77" t="n">
-        <v>52.27</v>
+        <v>521198</v>
+      </c>
+      <c r="F77" t="n">
+        <v>199313</v>
+      </c>
+      <c r="G77" t="n">
+        <v>38.24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>191.52</v>
+        <v>209.69</v>
       </c>
       <c r="C78" t="n">
-        <v>352994</v>
+        <v>209.69</v>
       </c>
       <c r="D78" t="n">
-        <v>145377</v>
+        <v>209.69</v>
       </c>
       <c r="E78" t="n">
-        <v>41.18</v>
+        <v>502208</v>
+      </c>
+      <c r="F78" t="n">
+        <v>211595</v>
+      </c>
+      <c r="G78" t="n">
+        <v>42.13</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>190.81</v>
+        <v>205.44</v>
       </c>
       <c r="C79" t="n">
-        <v>176529</v>
+        <v>205.44</v>
       </c>
       <c r="D79" t="n">
-        <v>79454</v>
+        <v>205.44</v>
       </c>
       <c r="E79" t="n">
-        <v>45.01</v>
+        <v>329991</v>
+      </c>
+      <c r="F79" t="n">
+        <v>144272</v>
+      </c>
+      <c r="G79" t="n">
+        <v>43.72</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>189.2</v>
+        <v>202.08</v>
       </c>
       <c r="C80" t="n">
-        <v>253213</v>
+        <v>202.08</v>
       </c>
       <c r="D80" t="n">
-        <v>99306</v>
+        <v>202.08</v>
       </c>
       <c r="E80" t="n">
-        <v>39.22</v>
+        <v>249041</v>
+      </c>
+      <c r="F80" t="n">
+        <v>119731</v>
+      </c>
+      <c r="G80" t="n">
+        <v>48.08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>185.83</v>
+        <v>192.83</v>
       </c>
       <c r="C81" t="n">
-        <v>136375</v>
+        <v>192.83</v>
       </c>
       <c r="D81" t="n">
-        <v>72726</v>
+        <v>192.83</v>
       </c>
       <c r="E81" t="n">
-        <v>53.33</v>
+        <v>500793</v>
+      </c>
+      <c r="F81" t="n">
+        <v>241258</v>
+      </c>
+      <c r="G81" t="n">
+        <v>48.18</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>191.23</v>
+        <v>195.07</v>
       </c>
       <c r="C82" t="n">
-        <v>184347</v>
+        <v>195.07</v>
       </c>
       <c r="D82" t="n">
-        <v>76044</v>
+        <v>195.07</v>
       </c>
       <c r="E82" t="n">
-        <v>41.25</v>
+        <v>460641</v>
+      </c>
+      <c r="F82" t="n">
+        <v>155739</v>
+      </c>
+      <c r="G82" t="n">
+        <v>33.81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>192.05</v>
+        <v>196.44</v>
       </c>
       <c r="C83" t="n">
-        <v>301266</v>
+        <v>196.44</v>
       </c>
       <c r="D83" t="n">
-        <v>131187</v>
+        <v>196.44</v>
       </c>
       <c r="E83" t="n">
-        <v>43.55</v>
+        <v>426004</v>
+      </c>
+      <c r="F83" t="n">
+        <v>170074</v>
+      </c>
+      <c r="G83" t="n">
+        <v>39.92</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>187.16</v>
+        <v>188.42</v>
       </c>
       <c r="C84" t="n">
-        <v>378971</v>
+        <v>188.42</v>
       </c>
       <c r="D84" t="n">
-        <v>160997</v>
+        <v>188.42</v>
       </c>
       <c r="E84" t="n">
-        <v>42.48</v>
+        <v>258634</v>
+      </c>
+      <c r="F84" t="n">
+        <v>145654</v>
+      </c>
+      <c r="G84" t="n">
+        <v>56.32</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>179.79</v>
+        <v>190.89</v>
       </c>
       <c r="C85" t="n">
-        <v>391792</v>
+        <v>190.89</v>
       </c>
       <c r="D85" t="n">
-        <v>218565</v>
+        <v>190.89</v>
       </c>
       <c r="E85" t="n">
-        <v>55.79</v>
+        <v>299700</v>
+      </c>
+      <c r="F85" t="n">
+        <v>84132</v>
+      </c>
+      <c r="G85" t="n">
+        <v>28.07</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>186.7</v>
+        <v>193.99</v>
       </c>
       <c r="C86" t="n">
-        <v>368213</v>
+        <v>193.99</v>
       </c>
       <c r="D86" t="n">
-        <v>140780</v>
+        <v>193.99</v>
       </c>
       <c r="E86" t="n">
-        <v>38.23</v>
+        <v>462891</v>
+      </c>
+      <c r="F86" t="n">
+        <v>179392</v>
+      </c>
+      <c r="G86" t="n">
+        <v>38.75</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>191.75</v>
+        <v>185.19</v>
       </c>
       <c r="C87" t="n">
-        <v>645175</v>
+        <v>185.19</v>
       </c>
       <c r="D87" t="n">
-        <v>172628</v>
+        <v>185.19</v>
       </c>
       <c r="E87" t="n">
-        <v>26.76</v>
+        <v>268484</v>
+      </c>
+      <c r="F87" t="n">
+        <v>136831</v>
+      </c>
+      <c r="G87" t="n">
+        <v>50.96</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>184.65</v>
+        <v>179.19</v>
       </c>
       <c r="C88" t="n">
-        <v>238978</v>
+        <v>179.19</v>
       </c>
       <c r="D88" t="n">
-        <v>139293</v>
+        <v>179.19</v>
       </c>
       <c r="E88" t="n">
-        <v>58.29</v>
+        <v>661747</v>
+      </c>
+      <c r="F88" t="n">
+        <v>290690</v>
+      </c>
+      <c r="G88" t="n">
+        <v>43.93</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>187.93</v>
+        <v>176.41</v>
       </c>
       <c r="C89" t="n">
-        <v>304101</v>
+        <v>176.41</v>
       </c>
       <c r="D89" t="n">
-        <v>115088</v>
+        <v>176.41</v>
       </c>
       <c r="E89" t="n">
-        <v>37.85</v>
+        <v>316517</v>
+      </c>
+      <c r="F89" t="n">
+        <v>129882</v>
+      </c>
+      <c r="G89" t="n">
+        <v>41.03</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>185.2</v>
+        <v>177.1</v>
       </c>
       <c r="C90" t="n">
-        <v>231737</v>
+        <v>177.1</v>
       </c>
       <c r="D90" t="n">
-        <v>104201</v>
+        <v>177.1</v>
       </c>
       <c r="E90" t="n">
-        <v>44.97</v>
+        <v>412362</v>
+      </c>
+      <c r="F90" t="n">
+        <v>147606</v>
+      </c>
+      <c r="G90" t="n">
+        <v>35.8</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>182.45</v>
+        <v>194.64</v>
       </c>
       <c r="C91" t="n">
-        <v>296419</v>
+        <v>194.64</v>
       </c>
       <c r="D91" t="n">
-        <v>118116</v>
+        <v>194.64</v>
       </c>
       <c r="E91" t="n">
-        <v>39.85</v>
+        <v>576845</v>
+      </c>
+      <c r="F91" t="n">
+        <v>237913</v>
+      </c>
+      <c r="G91" t="n">
+        <v>41.24</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>175.32</v>
+        <v>209.45</v>
       </c>
       <c r="C92" t="n">
-        <v>323857</v>
+        <v>209.45</v>
       </c>
       <c r="D92" t="n">
-        <v>183270</v>
+        <v>209.45</v>
       </c>
       <c r="E92" t="n">
-        <v>56.59</v>
+        <v>1052204</v>
+      </c>
+      <c r="F92" t="n">
+        <v>435585</v>
+      </c>
+      <c r="G92" t="n">
+        <v>41.4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>174.46</v>
+        <v>210.69</v>
       </c>
       <c r="C93" t="n">
-        <v>307465</v>
+        <v>210.69</v>
       </c>
       <c r="D93" t="n">
-        <v>139544</v>
+        <v>210.69</v>
       </c>
       <c r="E93" t="n">
-        <v>45.39</v>
+        <v>838992</v>
+      </c>
+      <c r="F93" t="n">
+        <v>328234</v>
+      </c>
+      <c r="G93" t="n">
+        <v>39.12</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>176.22</v>
+        <v>208.93</v>
       </c>
       <c r="C94" t="n">
-        <v>228441</v>
+        <v>208.93</v>
       </c>
       <c r="D94" t="n">
-        <v>89304</v>
+        <v>208.93</v>
       </c>
       <c r="E94" t="n">
-        <v>39.09</v>
+        <v>386562</v>
+      </c>
+      <c r="F94" t="n">
+        <v>185191</v>
+      </c>
+      <c r="G94" t="n">
+        <v>47.91</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>178.91</v>
+        <v>207.28</v>
       </c>
       <c r="C95" t="n">
-        <v>353105</v>
+        <v>207.28</v>
       </c>
       <c r="D95" t="n">
-        <v>181838</v>
+        <v>207.28</v>
       </c>
       <c r="E95" t="n">
-        <v>51.5</v>
+        <v>564864</v>
+      </c>
+      <c r="F95" t="n">
+        <v>268741</v>
+      </c>
+      <c r="G95" t="n">
+        <v>47.58</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>171.56</v>
+        <v>210.54</v>
       </c>
       <c r="C96" t="n">
-        <v>244937</v>
+        <v>210.54</v>
       </c>
       <c r="D96" t="n">
-        <v>129433</v>
+        <v>210.54</v>
       </c>
       <c r="E96" t="n">
-        <v>52.84</v>
+        <v>633248</v>
+      </c>
+      <c r="F96" t="n">
+        <v>280026</v>
+      </c>
+      <c r="G96" t="n">
+        <v>44.22</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>161.67</v>
+        <v>207.88</v>
       </c>
       <c r="C97" t="n">
-        <v>362699</v>
+        <v>207.88</v>
       </c>
       <c r="D97" t="n">
-        <v>190429</v>
+        <v>207.88</v>
       </c>
       <c r="E97" t="n">
-        <v>52.5</v>
+        <v>437781</v>
+      </c>
+      <c r="F97" t="n">
+        <v>204714</v>
+      </c>
+      <c r="G97" t="n">
+        <v>46.76</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>165.59</v>
+        <v>207.97</v>
       </c>
       <c r="C98" t="n">
-        <v>699855</v>
+        <v>207.97</v>
       </c>
       <c r="D98" t="n">
-        <v>382065</v>
+        <v>207.97</v>
       </c>
       <c r="E98" t="n">
-        <v>54.59</v>
+        <v>325213</v>
+      </c>
+      <c r="F98" t="n">
+        <v>155905</v>
+      </c>
+      <c r="G98" t="n">
+        <v>47.94</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>169.77</v>
+        <v>205.81</v>
       </c>
       <c r="C99" t="n">
-        <v>584141</v>
+        <v>205.81</v>
       </c>
       <c r="D99" t="n">
-        <v>286735</v>
+        <v>205.81</v>
       </c>
       <c r="E99" t="n">
-        <v>49.09</v>
+        <v>277804</v>
+      </c>
+      <c r="F99" t="n">
+        <v>148135</v>
+      </c>
+      <c r="G99" t="n">
+        <v>53.32</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>169.77</v>
+        <v>210.48</v>
       </c>
       <c r="C100" t="n">
-        <v>584141</v>
+        <v>210.48</v>
       </c>
       <c r="D100" t="n">
-        <v>286735</v>
+        <v>210.48</v>
       </c>
       <c r="E100" t="n">
-        <v>49.09</v>
+        <v>713509</v>
+      </c>
+      <c r="F100" t="n">
+        <v>312925</v>
+      </c>
+      <c r="G100" t="n">
+        <v>43.86</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>161.4</v>
+        <v>216.28</v>
       </c>
       <c r="C101" t="n">
-        <v>657534</v>
+        <v>216.28</v>
       </c>
       <c r="D101" t="n">
-        <v>379358</v>
+        <v>216.28</v>
       </c>
       <c r="E101" t="n">
-        <v>57.69</v>
+        <v>1228461</v>
+      </c>
+      <c r="F101" t="n">
+        <v>465074</v>
+      </c>
+      <c r="G101" t="n">
+        <v>37.86</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>151.7</v>
+        <v>218.9</v>
       </c>
       <c r="C102" t="n">
-        <v>529509</v>
+        <v>218.9</v>
       </c>
       <c r="D102" t="n">
-        <v>265808</v>
+        <v>218.9</v>
       </c>
       <c r="E102" t="n">
-        <v>50.2</v>
+        <v>1525947</v>
+      </c>
+      <c r="F102" t="n">
+        <v>512510</v>
+      </c>
+      <c r="G102" t="n">
+        <v>33.59</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>169.84</v>
+        <v>210.74</v>
       </c>
       <c r="C103" t="n">
-        <v>623246</v>
+        <v>210.74</v>
       </c>
       <c r="D103" t="n">
-        <v>236434</v>
+        <v>210.74</v>
       </c>
       <c r="E103" t="n">
-        <v>37.94</v>
+        <v>856011</v>
+      </c>
+      <c r="F103" t="n">
+        <v>347966</v>
+      </c>
+      <c r="G103" t="n">
+        <v>40.65</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>172.3</v>
+        <v>207.6</v>
       </c>
       <c r="C104" t="n">
-        <v>436534</v>
+        <v>207.6</v>
       </c>
       <c r="D104" t="n">
-        <v>167611</v>
+        <v>207.6</v>
       </c>
       <c r="E104" t="n">
-        <v>38.4</v>
+        <v>354286</v>
+      </c>
+      <c r="F104" t="n">
+        <v>188702</v>
+      </c>
+      <c r="G104" t="n">
+        <v>53.26</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>175.42</v>
+        <v>203.37</v>
       </c>
       <c r="C105" t="n">
-        <v>460106</v>
+        <v>203.37</v>
       </c>
       <c r="D105" t="n">
-        <v>135027</v>
+        <v>203.37</v>
       </c>
       <c r="E105" t="n">
-        <v>29.35</v>
+        <v>388598</v>
+      </c>
+      <c r="F105" t="n">
+        <v>211909</v>
+      </c>
+      <c r="G105" t="n">
+        <v>54.53</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>179.25</v>
+        <v>201.27</v>
       </c>
       <c r="C106" t="n">
-        <v>641007</v>
+        <v>201.27</v>
       </c>
       <c r="D106" t="n">
-        <v>185327</v>
+        <v>201.27</v>
       </c>
       <c r="E106" t="n">
-        <v>28.91</v>
+        <v>432530</v>
+      </c>
+      <c r="F106" t="n">
+        <v>197104</v>
+      </c>
+      <c r="G106" t="n">
+        <v>45.57</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>191.89</v>
+        <v>207.6</v>
       </c>
       <c r="C107" t="n">
-        <v>553785</v>
+        <v>207.6</v>
       </c>
       <c r="D107" t="n">
-        <v>265413</v>
+        <v>207.6</v>
       </c>
       <c r="E107" t="n">
-        <v>47.93</v>
+        <v>542506</v>
+      </c>
+      <c r="F107" t="n">
+        <v>206748</v>
+      </c>
+      <c r="G107" t="n">
+        <v>38.11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>190.9</v>
+        <v>219.29</v>
       </c>
       <c r="C108" t="n">
-        <v>450738</v>
+        <v>219.29</v>
       </c>
       <c r="D108" t="n">
-        <v>159743</v>
+        <v>219.29</v>
       </c>
       <c r="E108" t="n">
-        <v>35.44</v>
+        <v>1127807</v>
+      </c>
+      <c r="F108" t="n">
+        <v>534745</v>
+      </c>
+      <c r="G108" t="n">
+        <v>47.41</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>191.58</v>
+        <v>218.01</v>
       </c>
       <c r="C109" t="n">
-        <v>337108</v>
+        <v>218.01</v>
       </c>
       <c r="D109" t="n">
-        <v>161807</v>
+        <v>218.01</v>
       </c>
       <c r="E109" t="n">
-        <v>48</v>
+        <v>662535</v>
+      </c>
+      <c r="F109" t="n">
+        <v>327273</v>
+      </c>
+      <c r="G109" t="n">
+        <v>49.4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>192.01</v>
+        <v>236.17</v>
       </c>
       <c r="C110" t="n">
-        <v>523930</v>
+        <v>236.17</v>
       </c>
       <c r="D110" t="n">
-        <v>219520</v>
+        <v>236.17</v>
       </c>
       <c r="E110" t="n">
-        <v>41.9</v>
+        <v>5282930</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1218407</v>
+      </c>
+      <c r="G110" t="n">
+        <v>23.06</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>200.84</v>
+        <v>241.04</v>
       </c>
       <c r="C111" t="n">
-        <v>819587</v>
+        <v>241.04</v>
       </c>
       <c r="D111" t="n">
-        <v>403084</v>
+        <v>241.04</v>
       </c>
       <c r="E111" t="n">
-        <v>49.18</v>
+        <v>1337347</v>
+      </c>
+      <c r="F111" t="n">
+        <v>583281</v>
+      </c>
+      <c r="G111" t="n">
+        <v>43.61</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>207.07</v>
+        <v>234.23</v>
       </c>
       <c r="C112" t="n">
-        <v>895204</v>
+        <v>234.23</v>
       </c>
       <c r="D112" t="n">
-        <v>368672</v>
+        <v>234.23</v>
       </c>
       <c r="E112" t="n">
-        <v>41.18</v>
+        <v>758439</v>
+      </c>
+      <c r="F112" t="n">
+        <v>360626</v>
+      </c>
+      <c r="G112" t="n">
+        <v>47.55</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>208.56</v>
+        <v>231.02</v>
       </c>
       <c r="C113" t="n">
-        <v>506611</v>
+        <v>231.02</v>
       </c>
       <c r="D113" t="n">
-        <v>249714</v>
+        <v>231.02</v>
       </c>
       <c r="E113" t="n">
-        <v>49.29</v>
+        <v>677878</v>
+      </c>
+      <c r="F113" t="n">
+        <v>257581</v>
+      </c>
+      <c r="G113" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>206.91</v>
+        <v>232.95</v>
       </c>
       <c r="C114" t="n">
-        <v>433674</v>
+        <v>232.95</v>
       </c>
       <c r="D114" t="n">
-        <v>190552</v>
+        <v>232.95</v>
       </c>
       <c r="E114" t="n">
-        <v>43.94</v>
+        <v>1852558</v>
+      </c>
+      <c r="F114" t="n">
+        <v>424937</v>
+      </c>
+      <c r="G114" t="n">
+        <v>22.94</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>209.32</v>
+        <v>226.45</v>
       </c>
       <c r="C115" t="n">
-        <v>358324</v>
+        <v>226.45</v>
       </c>
       <c r="D115" t="n">
-        <v>178269</v>
+        <v>226.45</v>
       </c>
       <c r="E115" t="n">
-        <v>49.75</v>
+        <v>944872</v>
+      </c>
+      <c r="F115" t="n">
+        <v>350828</v>
+      </c>
+      <c r="G115" t="n">
+        <v>37.13</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>217.4</v>
+        <v>223.76</v>
       </c>
       <c r="C116" t="n">
-        <v>793933</v>
+        <v>223.76</v>
       </c>
       <c r="D116" t="n">
-        <v>340410</v>
+        <v>223.76</v>
       </c>
       <c r="E116" t="n">
-        <v>42.88</v>
+        <v>966670</v>
+      </c>
+      <c r="F116" t="n">
+        <v>238213</v>
+      </c>
+      <c r="G116" t="n">
+        <v>24.64</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>236.47</v>
+        <v>182.86</v>
       </c>
       <c r="C117" t="n">
-        <v>2973410</v>
+        <v>182.86</v>
       </c>
       <c r="D117" t="n">
-        <v>831701</v>
+        <v>182.86</v>
       </c>
       <c r="E117" t="n">
-        <v>27.97</v>
+        <v>189191</v>
+      </c>
+      <c r="F117" t="n">
+        <v>126528</v>
+      </c>
+      <c r="G117" t="n">
+        <v>66.88</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>224.71</v>
+        <v>187.15</v>
       </c>
       <c r="C118" t="n">
-        <v>768292</v>
+        <v>187.15</v>
       </c>
       <c r="D118" t="n">
-        <v>331088</v>
+        <v>187.15</v>
       </c>
       <c r="E118" t="n">
-        <v>43.09</v>
+        <v>293679</v>
+      </c>
+      <c r="F118" t="n">
+        <v>158795</v>
+      </c>
+      <c r="G118" t="n">
+        <v>54.07</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>229.56</v>
+        <v>191.72</v>
       </c>
       <c r="C119" t="n">
-        <v>477490</v>
+        <v>191.72</v>
       </c>
       <c r="D119" t="n">
-        <v>215632</v>
+        <v>191.72</v>
       </c>
       <c r="E119" t="n">
-        <v>45.16</v>
+        <v>540921</v>
+      </c>
+      <c r="F119" t="n">
+        <v>227301</v>
+      </c>
+      <c r="G119" t="n">
+        <v>42.02</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>235.06</v>
+        <v>196.81</v>
       </c>
       <c r="C120" t="n">
-        <v>656828</v>
+        <v>196.81</v>
       </c>
       <c r="D120" t="n">
-        <v>338366</v>
+        <v>196.81</v>
       </c>
       <c r="E120" t="n">
-        <v>51.52</v>
+        <v>419962</v>
+      </c>
+      <c r="F120" t="n">
+        <v>241578</v>
+      </c>
+      <c r="G120" t="n">
+        <v>57.52</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>232.63</v>
+        <v>201.67</v>
       </c>
       <c r="C121" t="n">
-        <v>430257</v>
+        <v>201.67</v>
       </c>
       <c r="D121" t="n">
-        <v>223412</v>
+        <v>201.67</v>
       </c>
       <c r="E121" t="n">
-        <v>51.93</v>
+        <v>444788</v>
+      </c>
+      <c r="F121" t="n">
+        <v>272631</v>
+      </c>
+      <c r="G121" t="n">
+        <v>61.29</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>229.3</v>
+        <v>198.42</v>
       </c>
       <c r="C122" t="n">
-        <v>258936</v>
+        <v>198.42</v>
       </c>
       <c r="D122" t="n">
-        <v>123900</v>
+        <v>198.42</v>
       </c>
       <c r="E122" t="n">
-        <v>47.85</v>
+        <v>298497</v>
+      </c>
+      <c r="F122" t="n">
+        <v>183893</v>
+      </c>
+      <c r="G122" t="n">
+        <v>61.61</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>232.96</v>
+        <v>207.2</v>
       </c>
       <c r="C123" t="n">
-        <v>271325</v>
+        <v>207.2</v>
       </c>
       <c r="D123" t="n">
-        <v>141037</v>
+        <v>207.2</v>
       </c>
       <c r="E123" t="n">
-        <v>51.98</v>
+        <v>987802</v>
+      </c>
+      <c r="F123" t="n">
+        <v>446501</v>
+      </c>
+      <c r="G123" t="n">
+        <v>45.2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>238.03</v>
+        <v>217.56</v>
       </c>
       <c r="C124" t="n">
-        <v>504985</v>
+        <v>217.56</v>
       </c>
       <c r="D124" t="n">
-        <v>224943</v>
+        <v>217.56</v>
       </c>
       <c r="E124" t="n">
-        <v>44.54</v>
+        <v>994252</v>
+      </c>
+      <c r="F124" t="n">
+        <v>617563</v>
+      </c>
+      <c r="G124" t="n">
+        <v>62.11</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>229.27</v>
+        <v>220.77</v>
       </c>
       <c r="C125" t="n">
-        <v>586873</v>
+        <v>220.77</v>
       </c>
       <c r="D125" t="n">
-        <v>314205</v>
+        <v>220.77</v>
       </c>
       <c r="E125" t="n">
-        <v>53.54</v>
+        <v>760663</v>
+      </c>
+      <c r="F125" t="n">
+        <v>427453</v>
+      </c>
+      <c r="G125" t="n">
+        <v>56.19</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>235.72</v>
+        <v>226.7</v>
       </c>
       <c r="C126" t="n">
-        <v>400928</v>
+        <v>226.7</v>
       </c>
       <c r="D126" t="n">
-        <v>232828</v>
+        <v>226.7</v>
       </c>
       <c r="E126" t="n">
-        <v>58.07</v>
+        <v>1583209</v>
+      </c>
+      <c r="F126" t="n">
+        <v>724582</v>
+      </c>
+      <c r="G126" t="n">
+        <v>45.77</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>242.92</v>
+        <v>217.98</v>
       </c>
       <c r="C127" t="n">
-        <v>1099175</v>
+        <v>217.98</v>
       </c>
       <c r="D127" t="n">
-        <v>565756</v>
+        <v>217.98</v>
       </c>
       <c r="E127" t="n">
-        <v>51.47</v>
+        <v>511092</v>
+      </c>
+      <c r="F127" t="n">
+        <v>272130</v>
+      </c>
+      <c r="G127" t="n">
+        <v>53.24</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>234.25</v>
+        <v>217.54</v>
       </c>
       <c r="C128" t="n">
-        <v>333630</v>
+        <v>217.54</v>
       </c>
       <c r="D128" t="n">
-        <v>168355</v>
+        <v>217.54</v>
       </c>
       <c r="E128" t="n">
-        <v>50.46</v>
+        <v>444681</v>
+      </c>
+      <c r="F128" t="n">
+        <v>195009</v>
+      </c>
+      <c r="G128" t="n">
+        <v>43.85</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>217.88</v>
+        <v>216.87</v>
       </c>
       <c r="C129" t="n">
-        <v>613717</v>
+        <v>216.87</v>
       </c>
       <c r="D129" t="n">
-        <v>349494</v>
+        <v>216.87</v>
       </c>
       <c r="E129" t="n">
-        <v>56.95</v>
+        <v>608168</v>
+      </c>
+      <c r="F129" t="n">
+        <v>222112</v>
+      </c>
+      <c r="G129" t="n">
+        <v>36.52</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>221.41</v>
+        <v>212.44</v>
       </c>
       <c r="C130" t="n">
-        <v>334921</v>
+        <v>212.44</v>
       </c>
       <c r="D130" t="n">
-        <v>147436</v>
+        <v>212.44</v>
       </c>
       <c r="E130" t="n">
-        <v>44.02</v>
+        <v>534968</v>
+      </c>
+      <c r="F130" t="n">
+        <v>289179</v>
+      </c>
+      <c r="G130" t="n">
+        <v>54.06</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>218.74</v>
+        <v>214.47</v>
       </c>
       <c r="C131" t="n">
-        <v>264413</v>
+        <v>214.47</v>
       </c>
       <c r="D131" t="n">
-        <v>134277</v>
+        <v>214.47</v>
       </c>
       <c r="E131" t="n">
-        <v>50.78</v>
+        <v>409351</v>
+      </c>
+      <c r="F131" t="n">
+        <v>223393</v>
+      </c>
+      <c r="G131" t="n">
+        <v>54.57</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>218.75</v>
+        <v>214.06</v>
       </c>
       <c r="C132" t="n">
-        <v>213028</v>
+        <v>214.06</v>
       </c>
       <c r="D132" t="n">
-        <v>101080</v>
+        <v>214.06</v>
       </c>
       <c r="E132" t="n">
-        <v>47.45</v>
+        <v>305308</v>
+      </c>
+      <c r="F132" t="n">
+        <v>161292</v>
+      </c>
+      <c r="G132" t="n">
+        <v>52.83</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>223.63</v>
+        <v>221.25</v>
       </c>
       <c r="C133" t="n">
-        <v>750298</v>
+        <v>221.25</v>
       </c>
       <c r="D133" t="n">
-        <v>242068</v>
+        <v>221.25</v>
       </c>
       <c r="E133" t="n">
-        <v>32.26</v>
+        <v>422142</v>
+      </c>
+      <c r="F133" t="n">
+        <v>255307</v>
+      </c>
+      <c r="G133" t="n">
+        <v>60.48</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>222.05</v>
+        <v>224.38</v>
       </c>
       <c r="C134" t="n">
-        <v>369565</v>
+        <v>224.38</v>
       </c>
       <c r="D134" t="n">
-        <v>155107</v>
+        <v>224.38</v>
       </c>
       <c r="E134" t="n">
-        <v>41.97</v>
+        <v>388613</v>
+      </c>
+      <c r="F134" t="n">
+        <v>210275</v>
+      </c>
+      <c r="G134" t="n">
+        <v>54.11</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>224.65</v>
+        <v>224.1</v>
       </c>
       <c r="C135" t="n">
-        <v>405461</v>
+        <v>224.1</v>
       </c>
       <c r="D135" t="n">
-        <v>167763</v>
+        <v>224.1</v>
       </c>
       <c r="E135" t="n">
-        <v>41.38</v>
+        <v>522799</v>
+      </c>
+      <c r="F135" t="n">
+        <v>277053</v>
+      </c>
+      <c r="G135" t="n">
+        <v>52.99</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>232.37</v>
+        <v>215.48</v>
       </c>
       <c r="C136" t="n">
-        <v>865734</v>
+        <v>215.48</v>
       </c>
       <c r="D136" t="n">
-        <v>366082</v>
+        <v>215.48</v>
       </c>
       <c r="E136" t="n">
-        <v>42.29</v>
+        <v>398403</v>
+      </c>
+      <c r="F136" t="n">
+        <v>239737</v>
+      </c>
+      <c r="G136" t="n">
+        <v>60.17</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>233.09</v>
+        <v>211.46</v>
       </c>
       <c r="C137" t="n">
-        <v>485126</v>
+        <v>211.46</v>
       </c>
       <c r="D137" t="n">
-        <v>217939</v>
+        <v>211.46</v>
       </c>
       <c r="E137" t="n">
-        <v>44.92</v>
+        <v>351883</v>
+      </c>
+      <c r="F137" t="n">
+        <v>214466</v>
+      </c>
+      <c r="G137" t="n">
+        <v>60.95</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>238.02</v>
+        <v>208.57</v>
       </c>
       <c r="C138" t="n">
-        <v>598944</v>
+        <v>208.57</v>
       </c>
       <c r="D138" t="n">
-        <v>279170</v>
+        <v>208.57</v>
       </c>
       <c r="E138" t="n">
-        <v>46.61</v>
+        <v>262221</v>
+      </c>
+      <c r="F138" t="n">
+        <v>159594</v>
+      </c>
+      <c r="G138" t="n">
+        <v>60.86</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>245.27</v>
+        <v>210.77</v>
       </c>
       <c r="C139" t="n">
-        <v>1302861</v>
+        <v>210.77</v>
       </c>
       <c r="D139" t="n">
-        <v>457206</v>
+        <v>210.77</v>
       </c>
       <c r="E139" t="n">
-        <v>35.09</v>
+        <v>300630</v>
+      </c>
+      <c r="F139" t="n">
+        <v>144815</v>
+      </c>
+      <c r="G139" t="n">
+        <v>48.17</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>247.92</v>
+        <v>203.66</v>
       </c>
       <c r="C140" t="n">
-        <v>1137256</v>
+        <v>203.66</v>
       </c>
       <c r="D140" t="n">
-        <v>525146</v>
+        <v>203.66</v>
       </c>
       <c r="E140" t="n">
-        <v>46.18</v>
+        <v>343762</v>
+      </c>
+      <c r="F140" t="n">
+        <v>168894</v>
+      </c>
+      <c r="G140" t="n">
+        <v>49.13</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>247.92</v>
+        <v>204.1</v>
       </c>
       <c r="C141" t="n">
-        <v>1137256</v>
+        <v>204.1</v>
       </c>
       <c r="D141" t="n">
-        <v>525146</v>
+        <v>204.1</v>
       </c>
       <c r="E141" t="n">
-        <v>46.18</v>
+        <v>284705</v>
+      </c>
+      <c r="F141" t="n">
+        <v>139540</v>
+      </c>
+      <c r="G141" t="n">
+        <v>49.01</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>268.94</v>
+        <v>220.55</v>
       </c>
       <c r="C142" t="n">
-        <v>6125091</v>
+        <v>220.55</v>
       </c>
       <c r="D142" t="n">
-        <v>1474260</v>
+        <v>220.55</v>
       </c>
       <c r="E142" t="n">
-        <v>24.07</v>
+        <v>1346966</v>
+      </c>
+      <c r="F142" t="n">
+        <v>556220</v>
+      </c>
+      <c r="G142" t="n">
+        <v>41.29</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>251.2</v>
+        <v>216.9</v>
       </c>
       <c r="C143" t="n">
-        <v>2410251</v>
+        <v>216.9</v>
       </c>
       <c r="D143" t="n">
-        <v>815257</v>
+        <v>216.9</v>
       </c>
       <c r="E143" t="n">
-        <v>33.82</v>
+        <v>375602</v>
+      </c>
+      <c r="F143" t="n">
+        <v>185093</v>
+      </c>
+      <c r="G143" t="n">
+        <v>49.28</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>258.1</v>
+        <v>228.75</v>
       </c>
       <c r="C144" t="n">
-        <v>1197837</v>
+        <v>228.75</v>
       </c>
       <c r="D144" t="n">
-        <v>461136</v>
+        <v>228.75</v>
       </c>
       <c r="E144" t="n">
-        <v>38.5</v>
+        <v>1783626</v>
+      </c>
+      <c r="F144" t="n">
+        <v>760574</v>
+      </c>
+      <c r="G144" t="n">
+        <v>42.64</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>252.45</v>
+        <v>224.97</v>
       </c>
       <c r="C145" t="n">
-        <v>866478</v>
+        <v>224.97</v>
       </c>
       <c r="D145" t="n">
-        <v>351846</v>
+        <v>224.97</v>
       </c>
       <c r="E145" t="n">
-        <v>40.61</v>
+        <v>362827</v>
+      </c>
+      <c r="F145" t="n">
+        <v>176479</v>
+      </c>
+      <c r="G145" t="n">
+        <v>48.64</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>250.15</v>
+        <v>229.76</v>
       </c>
       <c r="C146" t="n">
-        <v>700406</v>
+        <v>229.76</v>
       </c>
       <c r="D146" t="n">
-        <v>262039</v>
+        <v>229.76</v>
       </c>
       <c r="E146" t="n">
-        <v>37.41</v>
+        <v>252457</v>
+      </c>
+      <c r="F146" t="n">
+        <v>164123</v>
+      </c>
+      <c r="G146" t="n">
+        <v>65.01000000000001</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>231.95</v>
+        <v>234.97</v>
       </c>
       <c r="C147" t="n">
-        <v>672639</v>
+        <v>234.97</v>
       </c>
       <c r="D147" t="n">
-        <v>337152</v>
+        <v>234.97</v>
       </c>
       <c r="E147" t="n">
-        <v>50.12</v>
+        <v>1128549</v>
+      </c>
+      <c r="F147" t="n">
+        <v>664478</v>
+      </c>
+      <c r="G147" t="n">
+        <v>58.88</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>243.95</v>
+        <v>240.2</v>
       </c>
       <c r="C148" t="n">
-        <v>501191</v>
+        <v>240.2</v>
       </c>
       <c r="D148" t="n">
-        <v>198881</v>
+        <v>240.2</v>
       </c>
       <c r="E148" t="n">
-        <v>39.68</v>
+        <v>974026</v>
+      </c>
+      <c r="F148" t="n">
+        <v>420406</v>
+      </c>
+      <c r="G148" t="n">
+        <v>43.16</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>239.1</v>
+        <v>232.01</v>
       </c>
       <c r="C149" t="n">
-        <v>546827</v>
+        <v>232.01</v>
       </c>
       <c r="D149" t="n">
-        <v>222433</v>
+        <v>232.01</v>
       </c>
       <c r="E149" t="n">
-        <v>40.68</v>
+        <v>437664</v>
+      </c>
+      <c r="F149" t="n">
+        <v>242987</v>
+      </c>
+      <c r="G149" t="n">
+        <v>55.52</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>232.8</v>
+        <v>230.5</v>
       </c>
       <c r="C150" t="n">
-        <v>381732</v>
+        <v>230.5</v>
       </c>
       <c r="D150" t="n">
-        <v>150422</v>
+        <v>230.5</v>
       </c>
       <c r="E150" t="n">
-        <v>39.41</v>
+        <v>927614</v>
+      </c>
+      <c r="F150" t="n">
+        <v>511001</v>
+      </c>
+      <c r="G150" t="n">
+        <v>55.09</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>244.05</v>
+        <v>232.36</v>
       </c>
       <c r="C151" t="n">
-        <v>384447</v>
+        <v>232.36</v>
       </c>
       <c r="D151" t="n">
-        <v>160566</v>
+        <v>232.36</v>
       </c>
       <c r="E151" t="n">
-        <v>41.77</v>
+        <v>326992</v>
+      </c>
+      <c r="F151" t="n">
+        <v>136801</v>
+      </c>
+      <c r="G151" t="n">
+        <v>41.84</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>246.65</v>
+        <v>247.6</v>
       </c>
       <c r="C152" t="n">
-        <v>458056</v>
+        <v>247.6</v>
       </c>
       <c r="D152" t="n">
-        <v>223111</v>
+        <v>247.6</v>
       </c>
       <c r="E152" t="n">
-        <v>48.71</v>
+        <v>1408451</v>
+      </c>
+      <c r="F152" t="n">
+        <v>704104</v>
+      </c>
+      <c r="G152" t="n">
+        <v>49.99</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>261.55</v>
+        <v>250.65</v>
       </c>
       <c r="C153" t="n">
-        <v>1820380</v>
+        <v>250.65</v>
       </c>
       <c r="D153" t="n">
-        <v>698579</v>
+        <v>250.65</v>
       </c>
       <c r="E153" t="n">
-        <v>38.38</v>
+        <v>1092804</v>
+      </c>
+      <c r="F153" t="n">
+        <v>440046</v>
+      </c>
+      <c r="G153" t="n">
+        <v>40.27</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>264.65</v>
+        <v>240.85</v>
       </c>
       <c r="C154" t="n">
-        <v>759890</v>
+        <v>240.85</v>
       </c>
       <c r="D154" t="n">
-        <v>305549</v>
+        <v>240.85</v>
       </c>
       <c r="E154" t="n">
-        <v>40.21</v>
+        <v>496522</v>
+      </c>
+      <c r="F154" t="n">
+        <v>261677</v>
+      </c>
+      <c r="G154" t="n">
+        <v>52.7</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>261.5</v>
+        <v>245.7</v>
       </c>
       <c r="C155" t="n">
-        <v>578199</v>
+        <v>245.7</v>
       </c>
       <c r="D155" t="n">
-        <v>249257</v>
+        <v>245.7</v>
       </c>
       <c r="E155" t="n">
-        <v>43.11</v>
+        <v>1160210</v>
+      </c>
+      <c r="F155" t="n">
+        <v>390784</v>
+      </c>
+      <c r="G155" t="n">
+        <v>33.68</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>258.45</v>
+        <v>228.8</v>
       </c>
       <c r="C156" t="n">
-        <v>520331</v>
+        <v>228.8</v>
       </c>
       <c r="D156" t="n">
-        <v>244700</v>
+        <v>228.8</v>
       </c>
       <c r="E156" t="n">
-        <v>47.03</v>
+        <v>895722</v>
+      </c>
+      <c r="F156" t="n">
+        <v>520383</v>
+      </c>
+      <c r="G156" t="n">
+        <v>58.1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>269.9</v>
+        <v>232.55</v>
       </c>
       <c r="C157" t="n">
-        <v>1286785</v>
+        <v>232.55</v>
       </c>
       <c r="D157" t="n">
-        <v>495524</v>
+        <v>232.55</v>
       </c>
       <c r="E157" t="n">
-        <v>38.51</v>
+        <v>605195</v>
+      </c>
+      <c r="F157" t="n">
+        <v>247737</v>
+      </c>
+      <c r="G157" t="n">
+        <v>40.94</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>274.65</v>
+        <v>225.55</v>
       </c>
       <c r="C158" t="n">
-        <v>1788359</v>
+        <v>225.55</v>
       </c>
       <c r="D158" t="n">
-        <v>639682</v>
+        <v>225.55</v>
       </c>
       <c r="E158" t="n">
-        <v>35.77</v>
+        <v>328490</v>
+      </c>
+      <c r="F158" t="n">
+        <v>171432</v>
+      </c>
+      <c r="G158" t="n">
+        <v>52.19</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>275.15</v>
+        <v>237.2</v>
       </c>
       <c r="C159" t="n">
-        <v>3373490</v>
+        <v>237.2</v>
       </c>
       <c r="D159" t="n">
-        <v>859398</v>
+        <v>237.2</v>
       </c>
       <c r="E159" t="n">
-        <v>25.48</v>
+        <v>560337</v>
+      </c>
+      <c r="F159" t="n">
+        <v>284264</v>
+      </c>
+      <c r="G159" t="n">
+        <v>50.73</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>268.75</v>
+        <v>238.1</v>
       </c>
       <c r="C160" t="n">
-        <v>728136</v>
+        <v>238.1</v>
       </c>
       <c r="D160" t="n">
-        <v>304832</v>
+        <v>238.1</v>
       </c>
       <c r="E160" t="n">
-        <v>41.86</v>
+        <v>546596</v>
+      </c>
+      <c r="F160" t="n">
+        <v>252002</v>
+      </c>
+      <c r="G160" t="n">
+        <v>46.1</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>268.75</v>
+        <v>246.35</v>
       </c>
       <c r="C161" t="n">
-        <v>728136</v>
+        <v>246.35</v>
       </c>
       <c r="D161" t="n">
-        <v>304832</v>
+        <v>246.35</v>
       </c>
       <c r="E161" t="n">
-        <v>41.86</v>
+        <v>1642188</v>
+      </c>
+      <c r="F161" t="n">
+        <v>602486</v>
+      </c>
+      <c r="G161" t="n">
+        <v>36.69</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>273</v>
+        <v>250.2</v>
       </c>
       <c r="C162" t="n">
-        <v>910654</v>
+        <v>250.2</v>
       </c>
       <c r="D162" t="n">
-        <v>278689</v>
+        <v>250.2</v>
       </c>
       <c r="E162" t="n">
-        <v>30.6</v>
+        <v>601167</v>
+      </c>
+      <c r="F162" t="n">
+        <v>210362</v>
+      </c>
+      <c r="G162" t="n">
+        <v>34.99</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>283.55</v>
+        <v>247.35</v>
       </c>
       <c r="C163" t="n">
-        <v>983073</v>
+        <v>247.35</v>
       </c>
       <c r="D163" t="n">
-        <v>397886</v>
+        <v>247.35</v>
       </c>
       <c r="E163" t="n">
-        <v>40.47</v>
+        <v>367291</v>
+      </c>
+      <c r="F163" t="n">
+        <v>175436</v>
+      </c>
+      <c r="G163" t="n">
+        <v>47.76</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>290.95</v>
+        <v>245.8</v>
       </c>
       <c r="C164" t="n">
-        <v>979790</v>
+        <v>245.8</v>
       </c>
       <c r="D164" t="n">
-        <v>481859</v>
+        <v>245.8</v>
       </c>
       <c r="E164" t="n">
-        <v>49.18</v>
+        <v>290105</v>
+      </c>
+      <c r="F164" t="n">
+        <v>138406</v>
+      </c>
+      <c r="G164" t="n">
+        <v>47.71</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>284.2</v>
+        <v>252.6</v>
       </c>
       <c r="C165" t="n">
-        <v>676190</v>
+        <v>252.6</v>
       </c>
       <c r="D165" t="n">
-        <v>335816</v>
+        <v>252.6</v>
       </c>
       <c r="E165" t="n">
-        <v>49.66</v>
+        <v>662379</v>
+      </c>
+      <c r="F165" t="n">
+        <v>277940</v>
+      </c>
+      <c r="G165" t="n">
+        <v>41.96</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>280.3</v>
+        <v>245.75</v>
       </c>
       <c r="C166" t="n">
-        <v>681768</v>
+        <v>245.75</v>
       </c>
       <c r="D166" t="n">
-        <v>314632</v>
+        <v>245.75</v>
       </c>
       <c r="E166" t="n">
-        <v>46.15</v>
+        <v>359959</v>
+      </c>
+      <c r="F166" t="n">
+        <v>144988</v>
+      </c>
+      <c r="G166" t="n">
+        <v>40.28</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>275.95</v>
+        <v>240.15</v>
       </c>
       <c r="C167" t="n">
-        <v>543500</v>
+        <v>240.15</v>
       </c>
       <c r="D167" t="n">
-        <v>204959</v>
+        <v>240.15</v>
       </c>
       <c r="E167" t="n">
-        <v>37.71</v>
+        <v>436058</v>
+      </c>
+      <c r="F167" t="n">
+        <v>184140</v>
+      </c>
+      <c r="G167" t="n">
+        <v>42.23</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>254.25</v>
+        <v>227.95</v>
       </c>
       <c r="C168" t="n">
-        <v>1595288</v>
+        <v>227.95</v>
       </c>
       <c r="D168" t="n">
-        <v>726453</v>
+        <v>227.95</v>
       </c>
       <c r="E168" t="n">
-        <v>45.54</v>
+        <v>451228</v>
+      </c>
+      <c r="F168" t="n">
+        <v>235555</v>
+      </c>
+      <c r="G168" t="n">
+        <v>52.2</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>247.65</v>
+        <v>229.15</v>
       </c>
       <c r="C169" t="n">
-        <v>678579</v>
+        <v>229.15</v>
       </c>
       <c r="D169" t="n">
-        <v>288449</v>
+        <v>229.15</v>
       </c>
       <c r="E169" t="n">
-        <v>42.51</v>
+        <v>459443</v>
+      </c>
+      <c r="F169" t="n">
+        <v>147616</v>
+      </c>
+      <c r="G169" t="n">
+        <v>32.13</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>248.1</v>
+        <v>229.8</v>
       </c>
       <c r="C170" t="n">
-        <v>443836</v>
+        <v>229.8</v>
       </c>
       <c r="D170" t="n">
-        <v>185363</v>
+        <v>229.8</v>
       </c>
       <c r="E170" t="n">
-        <v>41.76</v>
+        <v>290799</v>
+      </c>
+      <c r="F170" t="n">
+        <v>94929</v>
+      </c>
+      <c r="G170" t="n">
+        <v>32.64</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>258.7</v>
+        <v>229.7</v>
       </c>
       <c r="C171" t="n">
-        <v>678920</v>
+        <v>229.7</v>
       </c>
       <c r="D171" t="n">
-        <v>282703</v>
+        <v>229.7</v>
       </c>
       <c r="E171" t="n">
-        <v>41.64</v>
+        <v>369715</v>
+      </c>
+      <c r="F171" t="n">
+        <v>134456</v>
+      </c>
+      <c r="G171" t="n">
+        <v>36.37</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>252.95</v>
+        <v>232.45</v>
       </c>
       <c r="C172" t="n">
-        <v>327831</v>
+        <v>232.45</v>
       </c>
       <c r="D172" t="n">
-        <v>179673</v>
+        <v>232.45</v>
       </c>
       <c r="E172" t="n">
-        <v>54.81</v>
+        <v>363084</v>
+      </c>
+      <c r="F172" t="n">
+        <v>142313</v>
+      </c>
+      <c r="G172" t="n">
+        <v>39.2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>255.2</v>
+        <v>232.35</v>
       </c>
       <c r="C173" t="n">
-        <v>804704</v>
+        <v>232.35</v>
       </c>
       <c r="D173" t="n">
-        <v>309458</v>
+        <v>232.35</v>
       </c>
       <c r="E173" t="n">
-        <v>38.46</v>
+        <v>508587</v>
+      </c>
+      <c r="F173" t="n">
+        <v>186435</v>
+      </c>
+      <c r="G173" t="n">
+        <v>36.66</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>255.95</v>
+        <v>221.78</v>
       </c>
       <c r="C174" t="n">
-        <v>646564</v>
+        <v>221.78</v>
       </c>
       <c r="D174" t="n">
-        <v>286372</v>
+        <v>221.78</v>
       </c>
       <c r="E174" t="n">
-        <v>44.29</v>
+        <v>527277</v>
+      </c>
+      <c r="F174" t="n">
+        <v>289410</v>
+      </c>
+      <c r="G174" t="n">
+        <v>54.89</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>253.4</v>
+        <v>215.08</v>
       </c>
       <c r="C175" t="n">
-        <v>378526</v>
+        <v>215.08</v>
       </c>
       <c r="D175" t="n">
-        <v>170908</v>
+        <v>215.08</v>
       </c>
       <c r="E175" t="n">
-        <v>45.15</v>
+        <v>287055</v>
+      </c>
+      <c r="F175" t="n">
+        <v>154073</v>
+      </c>
+      <c r="G175" t="n">
+        <v>53.67</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>249.75</v>
+        <v>211.41</v>
       </c>
       <c r="C176" t="n">
-        <v>384424</v>
+        <v>211.41</v>
       </c>
       <c r="D176" t="n">
-        <v>172951</v>
+        <v>211.41</v>
       </c>
       <c r="E176" t="n">
-        <v>44.99</v>
+        <v>306356</v>
+      </c>
+      <c r="F176" t="n">
+        <v>162763</v>
+      </c>
+      <c r="G176" t="n">
+        <v>53.13</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>254.6</v>
+        <v>207.12</v>
       </c>
       <c r="C177" t="n">
-        <v>326062</v>
+        <v>207.12</v>
       </c>
       <c r="D177" t="n">
-        <v>141094</v>
+        <v>207.12</v>
       </c>
       <c r="E177" t="n">
-        <v>43.27</v>
+        <v>216556</v>
+      </c>
+      <c r="F177" t="n">
+        <v>105994</v>
+      </c>
+      <c r="G177" t="n">
+        <v>48.95</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>260.6</v>
+        <v>200.06</v>
       </c>
       <c r="C178" t="n">
-        <v>739293</v>
+        <v>200.06</v>
       </c>
       <c r="D178" t="n">
-        <v>327878</v>
+        <v>200.06</v>
       </c>
       <c r="E178" t="n">
-        <v>44.35</v>
+        <v>306661</v>
+      </c>
+      <c r="F178" t="n">
+        <v>172316</v>
+      </c>
+      <c r="G178" t="n">
+        <v>56.19</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>255.5</v>
+        <v>205.41</v>
       </c>
       <c r="C179" t="n">
-        <v>529386</v>
+        <v>205.41</v>
       </c>
       <c r="D179" t="n">
-        <v>213169</v>
+        <v>205.41</v>
       </c>
       <c r="E179" t="n">
-        <v>40.27</v>
+        <v>457952</v>
+      </c>
+      <c r="F179" t="n">
+        <v>185687</v>
+      </c>
+      <c r="G179" t="n">
+        <v>40.55</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>247.85</v>
+        <v>201.55</v>
       </c>
       <c r="C180" t="n">
-        <v>340778</v>
+        <v>201.55</v>
       </c>
       <c r="D180" t="n">
-        <v>165641</v>
+        <v>201.55</v>
       </c>
       <c r="E180" t="n">
-        <v>48.61</v>
+        <v>227895</v>
+      </c>
+      <c r="F180" t="n">
+        <v>116405</v>
+      </c>
+      <c r="G180" t="n">
+        <v>51.08</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>254.8</v>
+        <v>203.44</v>
       </c>
       <c r="C181" t="n">
-        <v>1018743</v>
+        <v>203.44</v>
       </c>
       <c r="D181" t="n">
-        <v>275022</v>
+        <v>203.44</v>
       </c>
       <c r="E181" t="n">
-        <v>27</v>
+        <v>194751</v>
+      </c>
+      <c r="F181" t="n">
+        <v>71867</v>
+      </c>
+      <c r="G181" t="n">
+        <v>36.9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>269.95</v>
+        <v>202.89</v>
       </c>
       <c r="C182" t="n">
-        <v>1123801</v>
+        <v>202.89</v>
       </c>
       <c r="D182" t="n">
-        <v>479887</v>
+        <v>202.89</v>
       </c>
       <c r="E182" t="n">
-        <v>42.7</v>
+        <v>234838</v>
+      </c>
+      <c r="F182" t="n">
+        <v>111687</v>
+      </c>
+      <c r="G182" t="n">
+        <v>47.56</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>269.5</v>
+        <v>204.21</v>
       </c>
       <c r="C183" t="n">
-        <v>1003726</v>
+        <v>204.21</v>
       </c>
       <c r="D183" t="n">
-        <v>417336</v>
+        <v>204.21</v>
       </c>
       <c r="E183" t="n">
-        <v>41.58</v>
+        <v>138660</v>
+      </c>
+      <c r="F183" t="n">
+        <v>67811</v>
+      </c>
+      <c r="G183" t="n">
+        <v>48.9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>265.3</v>
+        <v>204.02</v>
       </c>
       <c r="C184" t="n">
-        <v>705596</v>
+        <v>204.02</v>
       </c>
       <c r="D184" t="n">
-        <v>341684</v>
+        <v>204.02</v>
       </c>
       <c r="E184" t="n">
-        <v>48.42</v>
+        <v>169974</v>
+      </c>
+      <c r="F184" t="n">
+        <v>87983</v>
+      </c>
+      <c r="G184" t="n">
+        <v>51.76</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>259.55</v>
+        <v>202.95</v>
       </c>
       <c r="C185" t="n">
-        <v>450813</v>
+        <v>202.95</v>
       </c>
       <c r="D185" t="n">
-        <v>197827</v>
+        <v>202.95</v>
       </c>
       <c r="E185" t="n">
-        <v>43.88</v>
+        <v>152367</v>
+      </c>
+      <c r="F185" t="n">
+        <v>97613</v>
+      </c>
+      <c r="G185" t="n">
+        <v>64.06</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>266</v>
+        <v>200.49</v>
       </c>
       <c r="C186" t="n">
-        <v>551731</v>
+        <v>200.49</v>
       </c>
       <c r="D186" t="n">
-        <v>260917</v>
+        <v>200.49</v>
       </c>
       <c r="E186" t="n">
-        <v>47.29</v>
+        <v>162147</v>
+      </c>
+      <c r="F186" t="n">
+        <v>87459</v>
+      </c>
+      <c r="G186" t="n">
+        <v>53.94</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>287.75</v>
+        <v>202.89</v>
       </c>
       <c r="C187" t="n">
-        <v>1548816</v>
+        <v>202.89</v>
       </c>
       <c r="D187" t="n">
-        <v>923218</v>
+        <v>202.89</v>
       </c>
       <c r="E187" t="n">
-        <v>59.61</v>
+        <v>138621</v>
+      </c>
+      <c r="F187" t="n">
+        <v>77492</v>
+      </c>
+      <c r="G187" t="n">
+        <v>55.9</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>300.6</v>
+        <v>216.23</v>
       </c>
       <c r="C188" t="n">
-        <v>3136932</v>
+        <v>216.23</v>
       </c>
       <c r="D188" t="n">
-        <v>1286085</v>
+        <v>216.23</v>
       </c>
       <c r="E188" t="n">
-        <v>41</v>
+        <v>590436</v>
+      </c>
+      <c r="F188" t="n">
+        <v>231348</v>
+      </c>
+      <c r="G188" t="n">
+        <v>39.18</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>305.5</v>
+        <v>213.31</v>
       </c>
       <c r="C189" t="n">
-        <v>1503289</v>
+        <v>213.31</v>
       </c>
       <c r="D189" t="n">
-        <v>661881</v>
+        <v>213.31</v>
       </c>
       <c r="E189" t="n">
-        <v>44.03</v>
+        <v>374031</v>
+      </c>
+      <c r="F189" t="n">
+        <v>112426</v>
+      </c>
+      <c r="G189" t="n">
+        <v>30.06</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>321.85</v>
+        <v>211.24</v>
       </c>
       <c r="C190" t="n">
-        <v>2276706</v>
+        <v>211.24</v>
       </c>
       <c r="D190" t="n">
-        <v>1189120</v>
+        <v>211.24</v>
       </c>
       <c r="E190" t="n">
-        <v>52.23</v>
+        <v>217216</v>
+      </c>
+      <c r="F190" t="n">
+        <v>79905</v>
+      </c>
+      <c r="G190" t="n">
+        <v>36.79</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>336.9</v>
+        <v>216.24</v>
       </c>
       <c r="C191" t="n">
-        <v>3869094</v>
+        <v>216.24</v>
       </c>
       <c r="D191" t="n">
-        <v>1596361</v>
+        <v>216.24</v>
       </c>
       <c r="E191" t="n">
-        <v>41.26</v>
+        <v>253191</v>
+      </c>
+      <c r="F191" t="n">
+        <v>117694</v>
+      </c>
+      <c r="G191" t="n">
+        <v>46.48</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>210.15</v>
+      </c>
+      <c r="C192" t="n">
+        <v>210.15</v>
+      </c>
+      <c r="D192" t="n">
+        <v>210.15</v>
+      </c>
+      <c r="E192" t="n">
+        <v>211126</v>
+      </c>
+      <c r="F192" t="n">
+        <v>110853</v>
+      </c>
+      <c r="G192" t="n">
+        <v>52.51</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>211.98</v>
+      </c>
+      <c r="C193" t="n">
+        <v>211.98</v>
+      </c>
+      <c r="D193" t="n">
+        <v>211.98</v>
+      </c>
+      <c r="E193" t="n">
+        <v>195490</v>
+      </c>
+      <c r="F193" t="n">
+        <v>74339</v>
+      </c>
+      <c r="G193" t="n">
+        <v>38.03</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>216.29</v>
+      </c>
+      <c r="C194" t="n">
+        <v>216.29</v>
+      </c>
+      <c r="D194" t="n">
+        <v>216.29</v>
+      </c>
+      <c r="E194" t="n">
+        <v>354659</v>
+      </c>
+      <c r="F194" t="n">
+        <v>144923</v>
+      </c>
+      <c r="G194" t="n">
+        <v>40.86</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>211.67</v>
+      </c>
+      <c r="C195" t="n">
+        <v>211.67</v>
+      </c>
+      <c r="D195" t="n">
+        <v>211.67</v>
+      </c>
+      <c r="E195" t="n">
+        <v>101318</v>
+      </c>
+      <c r="F195" t="n">
+        <v>59304</v>
+      </c>
+      <c r="G195" t="n">
+        <v>58.53</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>213.63</v>
+      </c>
+      <c r="C196" t="n">
+        <v>213.63</v>
+      </c>
+      <c r="D196" t="n">
+        <v>213.63</v>
+      </c>
+      <c r="E196" t="n">
+        <v>120850</v>
+      </c>
+      <c r="F196" t="n">
+        <v>60627</v>
+      </c>
+      <c r="G196" t="n">
+        <v>50.17</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>217.66</v>
+      </c>
+      <c r="C197" t="n">
+        <v>217.66</v>
+      </c>
+      <c r="D197" t="n">
+        <v>217.66</v>
+      </c>
+      <c r="E197" t="n">
+        <v>601320</v>
+      </c>
+      <c r="F197" t="n">
+        <v>203402</v>
+      </c>
+      <c r="G197" t="n">
+        <v>33.83</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>212.43</v>
+      </c>
+      <c r="C198" t="n">
+        <v>212.43</v>
+      </c>
+      <c r="D198" t="n">
+        <v>212.43</v>
+      </c>
+      <c r="E198" t="n">
+        <v>199360</v>
+      </c>
+      <c r="F198" t="n">
+        <v>109589</v>
+      </c>
+      <c r="G198" t="n">
+        <v>54.97</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>214.21</v>
+      </c>
+      <c r="C199" t="n">
+        <v>214.21</v>
+      </c>
+      <c r="D199" t="n">
+        <v>214.21</v>
+      </c>
+      <c r="E199" t="n">
+        <v>157933</v>
+      </c>
+      <c r="F199" t="n">
+        <v>67599</v>
+      </c>
+      <c r="G199" t="n">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>210.67</v>
+      </c>
+      <c r="C200" t="n">
+        <v>210.67</v>
+      </c>
+      <c r="D200" t="n">
+        <v>210.67</v>
+      </c>
+      <c r="E200" t="n">
+        <v>241715</v>
+      </c>
+      <c r="F200" t="n">
+        <v>126806</v>
+      </c>
+      <c r="G200" t="n">
+        <v>52.46</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>203.3</v>
+      </c>
+      <c r="C201" t="n">
+        <v>203.3</v>
+      </c>
+      <c r="D201" t="n">
+        <v>203.3</v>
+      </c>
+      <c r="E201" t="n">
+        <v>287667</v>
+      </c>
+      <c r="F201" t="n">
+        <v>115895</v>
+      </c>
+      <c r="G201" t="n">
+        <v>40.29</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>195.89</v>
+      </c>
+      <c r="C202" t="n">
+        <v>195.89</v>
+      </c>
+      <c r="D202" t="n">
+        <v>195.89</v>
+      </c>
+      <c r="E202" t="n">
+        <v>435697</v>
+      </c>
+      <c r="F202" t="n">
+        <v>191577</v>
+      </c>
+      <c r="G202" t="n">
+        <v>43.97</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>195.87</v>
+      </c>
+      <c r="C203" t="n">
+        <v>195.87</v>
+      </c>
+      <c r="D203" t="n">
+        <v>195.87</v>
+      </c>
+      <c r="E203" t="n">
+        <v>187258</v>
+      </c>
+      <c r="F203" t="n">
+        <v>89615</v>
+      </c>
+      <c r="G203" t="n">
+        <v>47.86</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>194.23</v>
+      </c>
+      <c r="C204" t="n">
+        <v>194.23</v>
+      </c>
+      <c r="D204" t="n">
+        <v>194.23</v>
+      </c>
+      <c r="E204" t="n">
+        <v>182447</v>
+      </c>
+      <c r="F204" t="n">
+        <v>95261</v>
+      </c>
+      <c r="G204" t="n">
+        <v>52.21</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>194.23</v>
+      </c>
+      <c r="C205" t="n">
+        <v>194.23</v>
+      </c>
+      <c r="D205" t="n">
+        <v>194.23</v>
+      </c>
+      <c r="E205" t="n">
+        <v>182447</v>
+      </c>
+      <c r="F205" t="n">
+        <v>95261</v>
+      </c>
+      <c r="G205" t="n">
+        <v>52.21</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="C206" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="D206" t="n">
+        <v>191.67</v>
+      </c>
+      <c r="E206" t="n">
+        <v>235150</v>
+      </c>
+      <c r="F206" t="n">
+        <v>129777</v>
+      </c>
+      <c r="G206" t="n">
+        <v>55.19</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="C207" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="D207" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="E207" t="n">
+        <v>320191</v>
+      </c>
+      <c r="F207" t="n">
+        <v>173126</v>
+      </c>
+      <c r="G207" t="n">
+        <v>54.07</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>176.14</v>
+      </c>
+      <c r="C208" t="n">
+        <v>176.14</v>
+      </c>
+      <c r="D208" t="n">
+        <v>176.14</v>
+      </c>
+      <c r="E208" t="n">
+        <v>507048</v>
+      </c>
+      <c r="F208" t="n">
+        <v>245388</v>
+      </c>
+      <c r="G208" t="n">
+        <v>48.4</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>175.96</v>
+      </c>
+      <c r="C209" t="n">
+        <v>175.96</v>
+      </c>
+      <c r="D209" t="n">
+        <v>175.96</v>
+      </c>
+      <c r="E209" t="n">
+        <v>287999</v>
+      </c>
+      <c r="F209" t="n">
+        <v>110660</v>
+      </c>
+      <c r="G209" t="n">
+        <v>38.42</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>182.18</v>
+      </c>
+      <c r="C210" t="n">
+        <v>182.18</v>
+      </c>
+      <c r="D210" t="n">
+        <v>182.18</v>
+      </c>
+      <c r="E210" t="n">
+        <v>181860</v>
+      </c>
+      <c r="F210" t="n">
+        <v>78358</v>
+      </c>
+      <c r="G210" t="n">
+        <v>43.09</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>170.49</v>
+      </c>
+      <c r="C211" t="n">
+        <v>170.49</v>
+      </c>
+      <c r="D211" t="n">
+        <v>170.49</v>
+      </c>
+      <c r="E211" t="n">
+        <v>457811</v>
+      </c>
+      <c r="F211" t="n">
+        <v>249785</v>
+      </c>
+      <c r="G211" t="n">
+        <v>54.56</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>182.28</v>
+      </c>
+      <c r="C212" t="n">
+        <v>182.28</v>
+      </c>
+      <c r="D212" t="n">
+        <v>182.28</v>
+      </c>
+      <c r="E212" t="n">
+        <v>891603</v>
+      </c>
+      <c r="F212" t="n">
+        <v>272563</v>
+      </c>
+      <c r="G212" t="n">
+        <v>30.57</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>180</v>
+      </c>
+      <c r="C213" t="n">
+        <v>180</v>
+      </c>
+      <c r="D213" t="n">
+        <v>180</v>
+      </c>
+      <c r="E213" t="n">
+        <v>462390</v>
+      </c>
+      <c r="F213" t="n">
+        <v>214096</v>
+      </c>
+      <c r="G213" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>176.53</v>
+      </c>
+      <c r="C214" t="n">
+        <v>176.53</v>
+      </c>
+      <c r="D214" t="n">
+        <v>176.53</v>
+      </c>
+      <c r="E214" t="n">
+        <v>360152</v>
+      </c>
+      <c r="F214" t="n">
+        <v>183516</v>
+      </c>
+      <c r="G214" t="n">
+        <v>50.96</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>180.41</v>
+      </c>
+      <c r="C215" t="n">
+        <v>180.41</v>
+      </c>
+      <c r="D215" t="n">
+        <v>180.41</v>
+      </c>
+      <c r="E215" t="n">
+        <v>384145</v>
+      </c>
+      <c r="F215" t="n">
+        <v>177674</v>
+      </c>
+      <c r="G215" t="n">
+        <v>46.25</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>186.37</v>
+      </c>
+      <c r="C216" t="n">
+        <v>186.37</v>
+      </c>
+      <c r="D216" t="n">
+        <v>186.37</v>
+      </c>
+      <c r="E216" t="n">
+        <v>439529</v>
+      </c>
+      <c r="F216" t="n">
+        <v>151394</v>
+      </c>
+      <c r="G216" t="n">
+        <v>34.44</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>194.24</v>
+      </c>
+      <c r="C217" t="n">
+        <v>194.24</v>
+      </c>
+      <c r="D217" t="n">
+        <v>194.24</v>
+      </c>
+      <c r="E217" t="n">
+        <v>519678</v>
+      </c>
+      <c r="F217" t="n">
+        <v>255199</v>
+      </c>
+      <c r="G217" t="n">
+        <v>49.11</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>194.59</v>
+      </c>
+      <c r="C218" t="n">
+        <v>194.59</v>
+      </c>
+      <c r="D218" t="n">
+        <v>194.59</v>
+      </c>
+      <c r="E218" t="n">
+        <v>298628</v>
+      </c>
+      <c r="F218" t="n">
+        <v>152194</v>
+      </c>
+      <c r="G218" t="n">
+        <v>50.96</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>190.91</v>
+      </c>
+      <c r="C219" t="n">
+        <v>190.91</v>
+      </c>
+      <c r="D219" t="n">
+        <v>190.91</v>
+      </c>
+      <c r="E219" t="n">
+        <v>157063</v>
+      </c>
+      <c r="F219" t="n">
+        <v>77781</v>
+      </c>
+      <c r="G219" t="n">
+        <v>49.52</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>188.14</v>
+      </c>
+      <c r="C220" t="n">
+        <v>188.14</v>
+      </c>
+      <c r="D220" t="n">
+        <v>188.14</v>
+      </c>
+      <c r="E220" t="n">
+        <v>151984</v>
+      </c>
+      <c r="F220" t="n">
+        <v>66045</v>
+      </c>
+      <c r="G220" t="n">
+        <v>43.46</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="C221" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="D221" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="E221" t="n">
+        <v>483315</v>
+      </c>
+      <c r="F221" t="n">
+        <v>247905</v>
+      </c>
+      <c r="G221" t="n">
+        <v>51.29</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>195.53</v>
+      </c>
+      <c r="C222" t="n">
+        <v>195.53</v>
+      </c>
+      <c r="D222" t="n">
+        <v>195.53</v>
+      </c>
+      <c r="E222" t="n">
+        <v>170928</v>
+      </c>
+      <c r="F222" t="n">
+        <v>97199</v>
+      </c>
+      <c r="G222" t="n">
+        <v>56.87</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="C223" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="D223" t="n">
+        <v>194.6</v>
+      </c>
+      <c r="E223" t="n">
+        <v>168385</v>
+      </c>
+      <c r="F223" t="n">
+        <v>94448</v>
+      </c>
+      <c r="G223" t="n">
+        <v>56.09</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>188.21</v>
+      </c>
+      <c r="C224" t="n">
+        <v>188.21</v>
+      </c>
+      <c r="D224" t="n">
+        <v>188.21</v>
+      </c>
+      <c r="E224" t="n">
+        <v>324228</v>
+      </c>
+      <c r="F224" t="n">
+        <v>146124</v>
+      </c>
+      <c r="G224" t="n">
+        <v>45.07</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>182.71</v>
+      </c>
+      <c r="C225" t="n">
+        <v>182.71</v>
+      </c>
+      <c r="D225" t="n">
+        <v>182.71</v>
+      </c>
+      <c r="E225" t="n">
+        <v>226167</v>
+      </c>
+      <c r="F225" t="n">
+        <v>99250</v>
+      </c>
+      <c r="G225" t="n">
+        <v>43.88</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>186.93</v>
+      </c>
+      <c r="C226" t="n">
+        <v>186.93</v>
+      </c>
+      <c r="D226" t="n">
+        <v>186.93</v>
+      </c>
+      <c r="E226" t="n">
+        <v>370128</v>
+      </c>
+      <c r="F226" t="n">
+        <v>130334</v>
+      </c>
+      <c r="G226" t="n">
+        <v>35.21</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="C227" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="D227" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="E227" t="n">
+        <v>494120</v>
+      </c>
+      <c r="F227" t="n">
+        <v>139895</v>
+      </c>
+      <c r="G227" t="n">
+        <v>28.31</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>195.25</v>
+      </c>
+      <c r="C228" t="n">
+        <v>195.25</v>
+      </c>
+      <c r="D228" t="n">
+        <v>195.25</v>
+      </c>
+      <c r="E228" t="n">
+        <v>392784</v>
+      </c>
+      <c r="F228" t="n">
+        <v>135586</v>
+      </c>
+      <c r="G228" t="n">
+        <v>34.52</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>188.84</v>
+      </c>
+      <c r="C229" t="n">
+        <v>188.84</v>
+      </c>
+      <c r="D229" t="n">
+        <v>188.84</v>
+      </c>
+      <c r="E229" t="n">
+        <v>203739</v>
+      </c>
+      <c r="F229" t="n">
+        <v>106485</v>
+      </c>
+      <c r="G229" t="n">
+        <v>52.27</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>191.52</v>
+      </c>
+      <c r="C230" t="n">
+        <v>191.52</v>
+      </c>
+      <c r="D230" t="n">
+        <v>191.52</v>
+      </c>
+      <c r="E230" t="n">
+        <v>352994</v>
+      </c>
+      <c r="F230" t="n">
+        <v>145377</v>
+      </c>
+      <c r="G230" t="n">
+        <v>41.18</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>190.81</v>
+      </c>
+      <c r="C231" t="n">
+        <v>190.81</v>
+      </c>
+      <c r="D231" t="n">
+        <v>190.81</v>
+      </c>
+      <c r="E231" t="n">
+        <v>176529</v>
+      </c>
+      <c r="F231" t="n">
+        <v>79454</v>
+      </c>
+      <c r="G231" t="n">
+        <v>45.01</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="C232" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="D232" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="E232" t="n">
+        <v>253213</v>
+      </c>
+      <c r="F232" t="n">
+        <v>99306</v>
+      </c>
+      <c r="G232" t="n">
+        <v>39.22</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>185.83</v>
+      </c>
+      <c r="C233" t="n">
+        <v>185.83</v>
+      </c>
+      <c r="D233" t="n">
+        <v>185.83</v>
+      </c>
+      <c r="E233" t="n">
+        <v>136375</v>
+      </c>
+      <c r="F233" t="n">
+        <v>72726</v>
+      </c>
+      <c r="G233" t="n">
+        <v>53.33</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>191.23</v>
+      </c>
+      <c r="C234" t="n">
+        <v>191.23</v>
+      </c>
+      <c r="D234" t="n">
+        <v>191.23</v>
+      </c>
+      <c r="E234" t="n">
+        <v>184347</v>
+      </c>
+      <c r="F234" t="n">
+        <v>76044</v>
+      </c>
+      <c r="G234" t="n">
+        <v>41.25</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>192.05</v>
+      </c>
+      <c r="C235" t="n">
+        <v>192.05</v>
+      </c>
+      <c r="D235" t="n">
+        <v>192.05</v>
+      </c>
+      <c r="E235" t="n">
+        <v>301266</v>
+      </c>
+      <c r="F235" t="n">
+        <v>131187</v>
+      </c>
+      <c r="G235" t="n">
+        <v>43.55</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>187.16</v>
+      </c>
+      <c r="C236" t="n">
+        <v>187.16</v>
+      </c>
+      <c r="D236" t="n">
+        <v>187.16</v>
+      </c>
+      <c r="E236" t="n">
+        <v>378971</v>
+      </c>
+      <c r="F236" t="n">
+        <v>160997</v>
+      </c>
+      <c r="G236" t="n">
+        <v>42.48</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>179.79</v>
+      </c>
+      <c r="C237" t="n">
+        <v>179.79</v>
+      </c>
+      <c r="D237" t="n">
+        <v>179.79</v>
+      </c>
+      <c r="E237" t="n">
+        <v>391792</v>
+      </c>
+      <c r="F237" t="n">
+        <v>218565</v>
+      </c>
+      <c r="G237" t="n">
+        <v>55.79</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="C238" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="D238" t="n">
+        <v>186.7</v>
+      </c>
+      <c r="E238" t="n">
+        <v>368213</v>
+      </c>
+      <c r="F238" t="n">
+        <v>140780</v>
+      </c>
+      <c r="G238" t="n">
+        <v>38.23</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>191.75</v>
+      </c>
+      <c r="C239" t="n">
+        <v>191.75</v>
+      </c>
+      <c r="D239" t="n">
+        <v>191.75</v>
+      </c>
+      <c r="E239" t="n">
+        <v>645175</v>
+      </c>
+      <c r="F239" t="n">
+        <v>172628</v>
+      </c>
+      <c r="G239" t="n">
+        <v>26.76</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>184.65</v>
+      </c>
+      <c r="C240" t="n">
+        <v>184.65</v>
+      </c>
+      <c r="D240" t="n">
+        <v>184.65</v>
+      </c>
+      <c r="E240" t="n">
+        <v>238978</v>
+      </c>
+      <c r="F240" t="n">
+        <v>139293</v>
+      </c>
+      <c r="G240" t="n">
+        <v>58.29</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>187.93</v>
+      </c>
+      <c r="C241" t="n">
+        <v>187.93</v>
+      </c>
+      <c r="D241" t="n">
+        <v>187.93</v>
+      </c>
+      <c r="E241" t="n">
+        <v>304101</v>
+      </c>
+      <c r="F241" t="n">
+        <v>115088</v>
+      </c>
+      <c r="G241" t="n">
+        <v>37.85</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="C242" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="D242" t="n">
+        <v>185.2</v>
+      </c>
+      <c r="E242" t="n">
+        <v>231737</v>
+      </c>
+      <c r="F242" t="n">
+        <v>104201</v>
+      </c>
+      <c r="G242" t="n">
+        <v>44.97</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>182.45</v>
+      </c>
+      <c r="C243" t="n">
+        <v>182.45</v>
+      </c>
+      <c r="D243" t="n">
+        <v>182.45</v>
+      </c>
+      <c r="E243" t="n">
+        <v>296419</v>
+      </c>
+      <c r="F243" t="n">
+        <v>118116</v>
+      </c>
+      <c r="G243" t="n">
+        <v>39.85</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>175.32</v>
+      </c>
+      <c r="C244" t="n">
+        <v>175.32</v>
+      </c>
+      <c r="D244" t="n">
+        <v>175.32</v>
+      </c>
+      <c r="E244" t="n">
+        <v>323857</v>
+      </c>
+      <c r="F244" t="n">
+        <v>183270</v>
+      </c>
+      <c r="G244" t="n">
+        <v>56.59</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>174.46</v>
+      </c>
+      <c r="C245" t="n">
+        <v>174.46</v>
+      </c>
+      <c r="D245" t="n">
+        <v>174.46</v>
+      </c>
+      <c r="E245" t="n">
+        <v>307465</v>
+      </c>
+      <c r="F245" t="n">
+        <v>139544</v>
+      </c>
+      <c r="G245" t="n">
+        <v>45.39</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>176.22</v>
+      </c>
+      <c r="C246" t="n">
+        <v>176.22</v>
+      </c>
+      <c r="D246" t="n">
+        <v>176.22</v>
+      </c>
+      <c r="E246" t="n">
+        <v>228441</v>
+      </c>
+      <c r="F246" t="n">
+        <v>89304</v>
+      </c>
+      <c r="G246" t="n">
+        <v>39.09</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>178.91</v>
+      </c>
+      <c r="C247" t="n">
+        <v>178.91</v>
+      </c>
+      <c r="D247" t="n">
+        <v>178.91</v>
+      </c>
+      <c r="E247" t="n">
+        <v>353105</v>
+      </c>
+      <c r="F247" t="n">
+        <v>181838</v>
+      </c>
+      <c r="G247" t="n">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>171.56</v>
+      </c>
+      <c r="C248" t="n">
+        <v>171.56</v>
+      </c>
+      <c r="D248" t="n">
+        <v>171.56</v>
+      </c>
+      <c r="E248" t="n">
+        <v>244937</v>
+      </c>
+      <c r="F248" t="n">
+        <v>129433</v>
+      </c>
+      <c r="G248" t="n">
+        <v>52.84</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>161.67</v>
+      </c>
+      <c r="C249" t="n">
+        <v>161.67</v>
+      </c>
+      <c r="D249" t="n">
+        <v>161.67</v>
+      </c>
+      <c r="E249" t="n">
+        <v>362699</v>
+      </c>
+      <c r="F249" t="n">
+        <v>190429</v>
+      </c>
+      <c r="G249" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>165.59</v>
+      </c>
+      <c r="C250" t="n">
+        <v>165.59</v>
+      </c>
+      <c r="D250" t="n">
+        <v>165.59</v>
+      </c>
+      <c r="E250" t="n">
+        <v>699855</v>
+      </c>
+      <c r="F250" t="n">
+        <v>382065</v>
+      </c>
+      <c r="G250" t="n">
+        <v>54.59</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>169.77</v>
+      </c>
+      <c r="C251" t="n">
+        <v>169.77</v>
+      </c>
+      <c r="D251" t="n">
+        <v>169.77</v>
+      </c>
+      <c r="E251" t="n">
+        <v>584141</v>
+      </c>
+      <c r="F251" t="n">
+        <v>286735</v>
+      </c>
+      <c r="G251" t="n">
+        <v>49.09</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>169.77</v>
+      </c>
+      <c r="C252" t="n">
+        <v>169.77</v>
+      </c>
+      <c r="D252" t="n">
+        <v>169.77</v>
+      </c>
+      <c r="E252" t="n">
+        <v>584141</v>
+      </c>
+      <c r="F252" t="n">
+        <v>286735</v>
+      </c>
+      <c r="G252" t="n">
+        <v>49.09</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="C253" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="D253" t="n">
+        <v>161.4</v>
+      </c>
+      <c r="E253" t="n">
+        <v>657534</v>
+      </c>
+      <c r="F253" t="n">
+        <v>379358</v>
+      </c>
+      <c r="G253" t="n">
+        <v>57.69</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>151.7</v>
+      </c>
+      <c r="C254" t="n">
+        <v>151.7</v>
+      </c>
+      <c r="D254" t="n">
+        <v>151.7</v>
+      </c>
+      <c r="E254" t="n">
+        <v>529509</v>
+      </c>
+      <c r="F254" t="n">
+        <v>265808</v>
+      </c>
+      <c r="G254" t="n">
+        <v>50.2</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>169.84</v>
+      </c>
+      <c r="C255" t="n">
+        <v>169.84</v>
+      </c>
+      <c r="D255" t="n">
+        <v>169.84</v>
+      </c>
+      <c r="E255" t="n">
+        <v>623246</v>
+      </c>
+      <c r="F255" t="n">
+        <v>236434</v>
+      </c>
+      <c r="G255" t="n">
+        <v>37.94</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="C256" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="D256" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="E256" t="n">
+        <v>436534</v>
+      </c>
+      <c r="F256" t="n">
+        <v>167611</v>
+      </c>
+      <c r="G256" t="n">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>175.42</v>
+      </c>
+      <c r="C257" t="n">
+        <v>175.42</v>
+      </c>
+      <c r="D257" t="n">
+        <v>175.42</v>
+      </c>
+      <c r="E257" t="n">
+        <v>460106</v>
+      </c>
+      <c r="F257" t="n">
+        <v>135027</v>
+      </c>
+      <c r="G257" t="n">
+        <v>29.35</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="C258" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="D258" t="n">
+        <v>179.25</v>
+      </c>
+      <c r="E258" t="n">
+        <v>641007</v>
+      </c>
+      <c r="F258" t="n">
+        <v>185327</v>
+      </c>
+      <c r="G258" t="n">
+        <v>28.91</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>191.89</v>
+      </c>
+      <c r="C259" t="n">
+        <v>191.89</v>
+      </c>
+      <c r="D259" t="n">
+        <v>191.89</v>
+      </c>
+      <c r="E259" t="n">
+        <v>553785</v>
+      </c>
+      <c r="F259" t="n">
+        <v>265413</v>
+      </c>
+      <c r="G259" t="n">
+        <v>47.93</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="C260" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="D260" t="n">
+        <v>190.9</v>
+      </c>
+      <c r="E260" t="n">
+        <v>450738</v>
+      </c>
+      <c r="F260" t="n">
+        <v>159743</v>
+      </c>
+      <c r="G260" t="n">
+        <v>35.44</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>191.58</v>
+      </c>
+      <c r="C261" t="n">
+        <v>191.58</v>
+      </c>
+      <c r="D261" t="n">
+        <v>191.58</v>
+      </c>
+      <c r="E261" t="n">
+        <v>337108</v>
+      </c>
+      <c r="F261" t="n">
+        <v>161807</v>
+      </c>
+      <c r="G261" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>192.01</v>
+      </c>
+      <c r="C262" t="n">
+        <v>192.01</v>
+      </c>
+      <c r="D262" t="n">
+        <v>192.01</v>
+      </c>
+      <c r="E262" t="n">
+        <v>523930</v>
+      </c>
+      <c r="F262" t="n">
+        <v>219520</v>
+      </c>
+      <c r="G262" t="n">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>200.84</v>
+      </c>
+      <c r="C263" t="n">
+        <v>200.84</v>
+      </c>
+      <c r="D263" t="n">
+        <v>200.84</v>
+      </c>
+      <c r="E263" t="n">
+        <v>819587</v>
+      </c>
+      <c r="F263" t="n">
+        <v>403084</v>
+      </c>
+      <c r="G263" t="n">
+        <v>49.18</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>207.07</v>
+      </c>
+      <c r="C264" t="n">
+        <v>207.07</v>
+      </c>
+      <c r="D264" t="n">
+        <v>207.07</v>
+      </c>
+      <c r="E264" t="n">
+        <v>895204</v>
+      </c>
+      <c r="F264" t="n">
+        <v>368672</v>
+      </c>
+      <c r="G264" t="n">
+        <v>41.18</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>208.56</v>
+      </c>
+      <c r="C265" t="n">
+        <v>208.56</v>
+      </c>
+      <c r="D265" t="n">
+        <v>208.56</v>
+      </c>
+      <c r="E265" t="n">
+        <v>506611</v>
+      </c>
+      <c r="F265" t="n">
+        <v>249714</v>
+      </c>
+      <c r="G265" t="n">
+        <v>49.29</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>206.91</v>
+      </c>
+      <c r="C266" t="n">
+        <v>206.91</v>
+      </c>
+      <c r="D266" t="n">
+        <v>206.91</v>
+      </c>
+      <c r="E266" t="n">
+        <v>433674</v>
+      </c>
+      <c r="F266" t="n">
+        <v>190552</v>
+      </c>
+      <c r="G266" t="n">
+        <v>43.94</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>209.32</v>
+      </c>
+      <c r="C267" t="n">
+        <v>209.32</v>
+      </c>
+      <c r="D267" t="n">
+        <v>209.32</v>
+      </c>
+      <c r="E267" t="n">
+        <v>358324</v>
+      </c>
+      <c r="F267" t="n">
+        <v>178269</v>
+      </c>
+      <c r="G267" t="n">
+        <v>49.75</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>217.4</v>
+      </c>
+      <c r="C268" t="n">
+        <v>217.4</v>
+      </c>
+      <c r="D268" t="n">
+        <v>217.4</v>
+      </c>
+      <c r="E268" t="n">
+        <v>793933</v>
+      </c>
+      <c r="F268" t="n">
+        <v>340410</v>
+      </c>
+      <c r="G268" t="n">
+        <v>42.88</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>236.47</v>
+      </c>
+      <c r="C269" t="n">
+        <v>236.47</v>
+      </c>
+      <c r="D269" t="n">
+        <v>236.47</v>
+      </c>
+      <c r="E269" t="n">
+        <v>2973410</v>
+      </c>
+      <c r="F269" t="n">
+        <v>831701</v>
+      </c>
+      <c r="G269" t="n">
+        <v>27.97</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>224.71</v>
+      </c>
+      <c r="C270" t="n">
+        <v>224.71</v>
+      </c>
+      <c r="D270" t="n">
+        <v>224.71</v>
+      </c>
+      <c r="E270" t="n">
+        <v>768292</v>
+      </c>
+      <c r="F270" t="n">
+        <v>331088</v>
+      </c>
+      <c r="G270" t="n">
+        <v>43.09</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>229.56</v>
+      </c>
+      <c r="C271" t="n">
+        <v>229.56</v>
+      </c>
+      <c r="D271" t="n">
+        <v>229.56</v>
+      </c>
+      <c r="E271" t="n">
+        <v>477490</v>
+      </c>
+      <c r="F271" t="n">
+        <v>215632</v>
+      </c>
+      <c r="G271" t="n">
+        <v>45.16</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>235.06</v>
+      </c>
+      <c r="C272" t="n">
+        <v>235.06</v>
+      </c>
+      <c r="D272" t="n">
+        <v>235.06</v>
+      </c>
+      <c r="E272" t="n">
+        <v>656828</v>
+      </c>
+      <c r="F272" t="n">
+        <v>338366</v>
+      </c>
+      <c r="G272" t="n">
+        <v>51.52</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>232.63</v>
+      </c>
+      <c r="C273" t="n">
+        <v>232.63</v>
+      </c>
+      <c r="D273" t="n">
+        <v>232.63</v>
+      </c>
+      <c r="E273" t="n">
+        <v>430257</v>
+      </c>
+      <c r="F273" t="n">
+        <v>223412</v>
+      </c>
+      <c r="G273" t="n">
+        <v>51.93</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>229.3</v>
+      </c>
+      <c r="C274" t="n">
+        <v>229.3</v>
+      </c>
+      <c r="D274" t="n">
+        <v>229.3</v>
+      </c>
+      <c r="E274" t="n">
+        <v>258936</v>
+      </c>
+      <c r="F274" t="n">
+        <v>123900</v>
+      </c>
+      <c r="G274" t="n">
+        <v>47.85</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>232.96</v>
+      </c>
+      <c r="C275" t="n">
+        <v>232.96</v>
+      </c>
+      <c r="D275" t="n">
+        <v>232.96</v>
+      </c>
+      <c r="E275" t="n">
+        <v>271325</v>
+      </c>
+      <c r="F275" t="n">
+        <v>141037</v>
+      </c>
+      <c r="G275" t="n">
+        <v>51.98</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>238.03</v>
+      </c>
+      <c r="C276" t="n">
+        <v>238.03</v>
+      </c>
+      <c r="D276" t="n">
+        <v>238.03</v>
+      </c>
+      <c r="E276" t="n">
+        <v>504985</v>
+      </c>
+      <c r="F276" t="n">
+        <v>224943</v>
+      </c>
+      <c r="G276" t="n">
+        <v>44.54</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>229.27</v>
+      </c>
+      <c r="C277" t="n">
+        <v>229.27</v>
+      </c>
+      <c r="D277" t="n">
+        <v>229.27</v>
+      </c>
+      <c r="E277" t="n">
+        <v>586873</v>
+      </c>
+      <c r="F277" t="n">
+        <v>314205</v>
+      </c>
+      <c r="G277" t="n">
+        <v>53.54</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>235.72</v>
+      </c>
+      <c r="C278" t="n">
+        <v>235.72</v>
+      </c>
+      <c r="D278" t="n">
+        <v>235.72</v>
+      </c>
+      <c r="E278" t="n">
+        <v>400928</v>
+      </c>
+      <c r="F278" t="n">
+        <v>232828</v>
+      </c>
+      <c r="G278" t="n">
+        <v>58.07</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>242.92</v>
+      </c>
+      <c r="C279" t="n">
+        <v>242.92</v>
+      </c>
+      <c r="D279" t="n">
+        <v>242.92</v>
+      </c>
+      <c r="E279" t="n">
+        <v>1099175</v>
+      </c>
+      <c r="F279" t="n">
+        <v>565756</v>
+      </c>
+      <c r="G279" t="n">
+        <v>51.47</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>234.25</v>
+      </c>
+      <c r="C280" t="n">
+        <v>234.25</v>
+      </c>
+      <c r="D280" t="n">
+        <v>234.25</v>
+      </c>
+      <c r="E280" t="n">
+        <v>333630</v>
+      </c>
+      <c r="F280" t="n">
+        <v>168355</v>
+      </c>
+      <c r="G280" t="n">
+        <v>50.46</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>217.88</v>
+      </c>
+      <c r="C281" t="n">
+        <v>217.88</v>
+      </c>
+      <c r="D281" t="n">
+        <v>217.88</v>
+      </c>
+      <c r="E281" t="n">
+        <v>613717</v>
+      </c>
+      <c r="F281" t="n">
+        <v>349494</v>
+      </c>
+      <c r="G281" t="n">
+        <v>56.95</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>221.41</v>
+      </c>
+      <c r="C282" t="n">
+        <v>221.41</v>
+      </c>
+      <c r="D282" t="n">
+        <v>221.41</v>
+      </c>
+      <c r="E282" t="n">
+        <v>334921</v>
+      </c>
+      <c r="F282" t="n">
+        <v>147436</v>
+      </c>
+      <c r="G282" t="n">
+        <v>44.02</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>218.74</v>
+      </c>
+      <c r="C283" t="n">
+        <v>218.74</v>
+      </c>
+      <c r="D283" t="n">
+        <v>218.74</v>
+      </c>
+      <c r="E283" t="n">
+        <v>264413</v>
+      </c>
+      <c r="F283" t="n">
+        <v>134277</v>
+      </c>
+      <c r="G283" t="n">
+        <v>50.78</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="C284" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="D284" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="E284" t="n">
+        <v>213028</v>
+      </c>
+      <c r="F284" t="n">
+        <v>101080</v>
+      </c>
+      <c r="G284" t="n">
+        <v>47.45</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>223.63</v>
+      </c>
+      <c r="C285" t="n">
+        <v>223.63</v>
+      </c>
+      <c r="D285" t="n">
+        <v>223.63</v>
+      </c>
+      <c r="E285" t="n">
+        <v>750298</v>
+      </c>
+      <c r="F285" t="n">
+        <v>242068</v>
+      </c>
+      <c r="G285" t="n">
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>222.05</v>
+      </c>
+      <c r="C286" t="n">
+        <v>222.05</v>
+      </c>
+      <c r="D286" t="n">
+        <v>222.05</v>
+      </c>
+      <c r="E286" t="n">
+        <v>369565</v>
+      </c>
+      <c r="F286" t="n">
+        <v>155107</v>
+      </c>
+      <c r="G286" t="n">
+        <v>41.97</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>224.65</v>
+      </c>
+      <c r="C287" t="n">
+        <v>224.65</v>
+      </c>
+      <c r="D287" t="n">
+        <v>224.65</v>
+      </c>
+      <c r="E287" t="n">
+        <v>405461</v>
+      </c>
+      <c r="F287" t="n">
+        <v>167763</v>
+      </c>
+      <c r="G287" t="n">
+        <v>41.38</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>232.37</v>
+      </c>
+      <c r="C288" t="n">
+        <v>232.37</v>
+      </c>
+      <c r="D288" t="n">
+        <v>232.37</v>
+      </c>
+      <c r="E288" t="n">
+        <v>865734</v>
+      </c>
+      <c r="F288" t="n">
+        <v>366082</v>
+      </c>
+      <c r="G288" t="n">
+        <v>42.29</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>233.09</v>
+      </c>
+      <c r="C289" t="n">
+        <v>233.09</v>
+      </c>
+      <c r="D289" t="n">
+        <v>233.09</v>
+      </c>
+      <c r="E289" t="n">
+        <v>485126</v>
+      </c>
+      <c r="F289" t="n">
+        <v>217939</v>
+      </c>
+      <c r="G289" t="n">
+        <v>44.92</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>238.02</v>
+      </c>
+      <c r="C290" t="n">
+        <v>238.02</v>
+      </c>
+      <c r="D290" t="n">
+        <v>238.02</v>
+      </c>
+      <c r="E290" t="n">
+        <v>598944</v>
+      </c>
+      <c r="F290" t="n">
+        <v>279170</v>
+      </c>
+      <c r="G290" t="n">
+        <v>46.61</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B291" t="n">
+        <v>245.27</v>
+      </c>
+      <c r="C291" t="n">
+        <v>245.27</v>
+      </c>
+      <c r="D291" t="n">
+        <v>245.27</v>
+      </c>
+      <c r="E291" t="n">
+        <v>1302861</v>
+      </c>
+      <c r="F291" t="n">
+        <v>457206</v>
+      </c>
+      <c r="G291" t="n">
+        <v>35.09</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B292" t="n">
+        <v>247.92</v>
+      </c>
+      <c r="C292" t="n">
+        <v>247.92</v>
+      </c>
+      <c r="D292" t="n">
+        <v>247.92</v>
+      </c>
+      <c r="E292" t="n">
+        <v>1137256</v>
+      </c>
+      <c r="F292" t="n">
+        <v>525146</v>
+      </c>
+      <c r="G292" t="n">
+        <v>46.18</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B293" t="n">
+        <v>247.92</v>
+      </c>
+      <c r="C293" t="n">
+        <v>247.92</v>
+      </c>
+      <c r="D293" t="n">
+        <v>247.92</v>
+      </c>
+      <c r="E293" t="n">
+        <v>1137256</v>
+      </c>
+      <c r="F293" t="n">
+        <v>525146</v>
+      </c>
+      <c r="G293" t="n">
+        <v>46.18</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>268.94</v>
+      </c>
+      <c r="C294" t="n">
+        <v>268.94</v>
+      </c>
+      <c r="D294" t="n">
+        <v>268.94</v>
+      </c>
+      <c r="E294" t="n">
+        <v>6125091</v>
+      </c>
+      <c r="F294" t="n">
+        <v>1474260</v>
+      </c>
+      <c r="G294" t="n">
+        <v>24.07</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>251.2</v>
+      </c>
+      <c r="C295" t="n">
+        <v>251.2</v>
+      </c>
+      <c r="D295" t="n">
+        <v>251.2</v>
+      </c>
+      <c r="E295" t="n">
+        <v>2410251</v>
+      </c>
+      <c r="F295" t="n">
+        <v>815257</v>
+      </c>
+      <c r="G295" t="n">
+        <v>33.82</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>258.1</v>
+      </c>
+      <c r="C296" t="n">
+        <v>258.1</v>
+      </c>
+      <c r="D296" t="n">
+        <v>258.1</v>
+      </c>
+      <c r="E296" t="n">
+        <v>1197837</v>
+      </c>
+      <c r="F296" t="n">
+        <v>461136</v>
+      </c>
+      <c r="G296" t="n">
+        <v>38.5</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>252.45</v>
+      </c>
+      <c r="C297" t="n">
+        <v>252.45</v>
+      </c>
+      <c r="D297" t="n">
+        <v>252.45</v>
+      </c>
+      <c r="E297" t="n">
+        <v>866478</v>
+      </c>
+      <c r="F297" t="n">
+        <v>351846</v>
+      </c>
+      <c r="G297" t="n">
+        <v>40.61</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>250.15</v>
+      </c>
+      <c r="C298" t="n">
+        <v>250.15</v>
+      </c>
+      <c r="D298" t="n">
+        <v>250.15</v>
+      </c>
+      <c r="E298" t="n">
+        <v>700406</v>
+      </c>
+      <c r="F298" t="n">
+        <v>262039</v>
+      </c>
+      <c r="G298" t="n">
+        <v>37.41</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B299" t="n">
+        <v>231.95</v>
+      </c>
+      <c r="C299" t="n">
+        <v>231.95</v>
+      </c>
+      <c r="D299" t="n">
+        <v>231.95</v>
+      </c>
+      <c r="E299" t="n">
+        <v>672639</v>
+      </c>
+      <c r="F299" t="n">
+        <v>337152</v>
+      </c>
+      <c r="G299" t="n">
+        <v>50.12</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>243.95</v>
+      </c>
+      <c r="C300" t="n">
+        <v>243.95</v>
+      </c>
+      <c r="D300" t="n">
+        <v>243.95</v>
+      </c>
+      <c r="E300" t="n">
+        <v>501191</v>
+      </c>
+      <c r="F300" t="n">
+        <v>198881</v>
+      </c>
+      <c r="G300" t="n">
+        <v>39.68</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>239.1</v>
+      </c>
+      <c r="C301" t="n">
+        <v>239.1</v>
+      </c>
+      <c r="D301" t="n">
+        <v>239.1</v>
+      </c>
+      <c r="E301" t="n">
+        <v>546827</v>
+      </c>
+      <c r="F301" t="n">
+        <v>222433</v>
+      </c>
+      <c r="G301" t="n">
+        <v>40.68</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="C302" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="D302" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="E302" t="n">
+        <v>381732</v>
+      </c>
+      <c r="F302" t="n">
+        <v>150422</v>
+      </c>
+      <c r="G302" t="n">
+        <v>39.41</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>244.05</v>
+      </c>
+      <c r="C303" t="n">
+        <v>244.05</v>
+      </c>
+      <c r="D303" t="n">
+        <v>244.05</v>
+      </c>
+      <c r="E303" t="n">
+        <v>384447</v>
+      </c>
+      <c r="F303" t="n">
+        <v>160566</v>
+      </c>
+      <c r="G303" t="n">
+        <v>41.77</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>246.65</v>
+      </c>
+      <c r="C304" t="n">
+        <v>246.65</v>
+      </c>
+      <c r="D304" t="n">
+        <v>246.65</v>
+      </c>
+      <c r="E304" t="n">
+        <v>458056</v>
+      </c>
+      <c r="F304" t="n">
+        <v>223111</v>
+      </c>
+      <c r="G304" t="n">
+        <v>48.71</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B305" t="n">
+        <v>261.55</v>
+      </c>
+      <c r="C305" t="n">
+        <v>261.55</v>
+      </c>
+      <c r="D305" t="n">
+        <v>261.55</v>
+      </c>
+      <c r="E305" t="n">
+        <v>1820380</v>
+      </c>
+      <c r="F305" t="n">
+        <v>698579</v>
+      </c>
+      <c r="G305" t="n">
+        <v>38.38</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B306" t="n">
+        <v>264.65</v>
+      </c>
+      <c r="C306" t="n">
+        <v>264.65</v>
+      </c>
+      <c r="D306" t="n">
+        <v>264.65</v>
+      </c>
+      <c r="E306" t="n">
+        <v>759890</v>
+      </c>
+      <c r="F306" t="n">
+        <v>305549</v>
+      </c>
+      <c r="G306" t="n">
+        <v>40.21</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="C307" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="D307" t="n">
+        <v>261.5</v>
+      </c>
+      <c r="E307" t="n">
+        <v>578199</v>
+      </c>
+      <c r="F307" t="n">
+        <v>249257</v>
+      </c>
+      <c r="G307" t="n">
+        <v>43.11</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B308" t="n">
+        <v>258.45</v>
+      </c>
+      <c r="C308" t="n">
+        <v>258.45</v>
+      </c>
+      <c r="D308" t="n">
+        <v>258.45</v>
+      </c>
+      <c r="E308" t="n">
+        <v>520331</v>
+      </c>
+      <c r="F308" t="n">
+        <v>244700</v>
+      </c>
+      <c r="G308" t="n">
+        <v>47.03</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="C309" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="D309" t="n">
+        <v>269.9</v>
+      </c>
+      <c r="E309" t="n">
+        <v>1286785</v>
+      </c>
+      <c r="F309" t="n">
+        <v>495524</v>
+      </c>
+      <c r="G309" t="n">
+        <v>38.51</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>274.65</v>
+      </c>
+      <c r="C310" t="n">
+        <v>274.65</v>
+      </c>
+      <c r="D310" t="n">
+        <v>274.65</v>
+      </c>
+      <c r="E310" t="n">
+        <v>1788359</v>
+      </c>
+      <c r="F310" t="n">
+        <v>639682</v>
+      </c>
+      <c r="G310" t="n">
+        <v>35.77</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B311" t="n">
+        <v>275.15</v>
+      </c>
+      <c r="C311" t="n">
+        <v>275.15</v>
+      </c>
+      <c r="D311" t="n">
+        <v>275.15</v>
+      </c>
+      <c r="E311" t="n">
+        <v>3373490</v>
+      </c>
+      <c r="F311" t="n">
+        <v>859398</v>
+      </c>
+      <c r="G311" t="n">
+        <v>25.48</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>268.75</v>
+      </c>
+      <c r="C312" t="n">
+        <v>268.75</v>
+      </c>
+      <c r="D312" t="n">
+        <v>268.75</v>
+      </c>
+      <c r="E312" t="n">
+        <v>728136</v>
+      </c>
+      <c r="F312" t="n">
+        <v>304832</v>
+      </c>
+      <c r="G312" t="n">
+        <v>41.86</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>268.75</v>
+      </c>
+      <c r="C313" t="n">
+        <v>268.75</v>
+      </c>
+      <c r="D313" t="n">
+        <v>268.75</v>
+      </c>
+      <c r="E313" t="n">
+        <v>728136</v>
+      </c>
+      <c r="F313" t="n">
+        <v>304832</v>
+      </c>
+      <c r="G313" t="n">
+        <v>41.86</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>273</v>
+      </c>
+      <c r="C314" t="n">
+        <v>273</v>
+      </c>
+      <c r="D314" t="n">
+        <v>273</v>
+      </c>
+      <c r="E314" t="n">
+        <v>910654</v>
+      </c>
+      <c r="F314" t="n">
+        <v>278689</v>
+      </c>
+      <c r="G314" t="n">
+        <v>30.6</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B315" t="n">
+        <v>283.55</v>
+      </c>
+      <c r="C315" t="n">
+        <v>283.55</v>
+      </c>
+      <c r="D315" t="n">
+        <v>283.55</v>
+      </c>
+      <c r="E315" t="n">
+        <v>983073</v>
+      </c>
+      <c r="F315" t="n">
+        <v>397886</v>
+      </c>
+      <c r="G315" t="n">
+        <v>40.47</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>290.95</v>
+      </c>
+      <c r="C316" t="n">
+        <v>290.95</v>
+      </c>
+      <c r="D316" t="n">
+        <v>290.95</v>
+      </c>
+      <c r="E316" t="n">
+        <v>979790</v>
+      </c>
+      <c r="F316" t="n">
+        <v>481859</v>
+      </c>
+      <c r="G316" t="n">
+        <v>49.18</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>284.2</v>
+      </c>
+      <c r="C317" t="n">
+        <v>284.2</v>
+      </c>
+      <c r="D317" t="n">
+        <v>284.2</v>
+      </c>
+      <c r="E317" t="n">
+        <v>676190</v>
+      </c>
+      <c r="F317" t="n">
+        <v>335816</v>
+      </c>
+      <c r="G317" t="n">
+        <v>49.66</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>280.3</v>
+      </c>
+      <c r="C318" t="n">
+        <v>280.3</v>
+      </c>
+      <c r="D318" t="n">
+        <v>280.3</v>
+      </c>
+      <c r="E318" t="n">
+        <v>681768</v>
+      </c>
+      <c r="F318" t="n">
+        <v>314632</v>
+      </c>
+      <c r="G318" t="n">
+        <v>46.15</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>275.95</v>
+      </c>
+      <c r="C319" t="n">
+        <v>275.95</v>
+      </c>
+      <c r="D319" t="n">
+        <v>275.95</v>
+      </c>
+      <c r="E319" t="n">
+        <v>543500</v>
+      </c>
+      <c r="F319" t="n">
+        <v>204959</v>
+      </c>
+      <c r="G319" t="n">
+        <v>37.71</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>254.25</v>
+      </c>
+      <c r="C320" t="n">
+        <v>254.25</v>
+      </c>
+      <c r="D320" t="n">
+        <v>254.25</v>
+      </c>
+      <c r="E320" t="n">
+        <v>1595288</v>
+      </c>
+      <c r="F320" t="n">
+        <v>726453</v>
+      </c>
+      <c r="G320" t="n">
+        <v>45.54</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>247.65</v>
+      </c>
+      <c r="C321" t="n">
+        <v>247.65</v>
+      </c>
+      <c r="D321" t="n">
+        <v>247.65</v>
+      </c>
+      <c r="E321" t="n">
+        <v>678579</v>
+      </c>
+      <c r="F321" t="n">
+        <v>288449</v>
+      </c>
+      <c r="G321" t="n">
+        <v>42.51</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="C322" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="D322" t="n">
+        <v>248.1</v>
+      </c>
+      <c r="E322" t="n">
+        <v>443836</v>
+      </c>
+      <c r="F322" t="n">
+        <v>185363</v>
+      </c>
+      <c r="G322" t="n">
+        <v>41.76</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>258.7</v>
+      </c>
+      <c r="C323" t="n">
+        <v>258.7</v>
+      </c>
+      <c r="D323" t="n">
+        <v>258.7</v>
+      </c>
+      <c r="E323" t="n">
+        <v>678920</v>
+      </c>
+      <c r="F323" t="n">
+        <v>282703</v>
+      </c>
+      <c r="G323" t="n">
+        <v>41.64</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>252.95</v>
+      </c>
+      <c r="C324" t="n">
+        <v>252.95</v>
+      </c>
+      <c r="D324" t="n">
+        <v>252.95</v>
+      </c>
+      <c r="E324" t="n">
+        <v>327831</v>
+      </c>
+      <c r="F324" t="n">
+        <v>179673</v>
+      </c>
+      <c r="G324" t="n">
+        <v>54.81</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="C325" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="D325" t="n">
+        <v>255.2</v>
+      </c>
+      <c r="E325" t="n">
+        <v>804704</v>
+      </c>
+      <c r="F325" t="n">
+        <v>309458</v>
+      </c>
+      <c r="G325" t="n">
+        <v>38.46</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>255.95</v>
+      </c>
+      <c r="C326" t="n">
+        <v>255.95</v>
+      </c>
+      <c r="D326" t="n">
+        <v>255.95</v>
+      </c>
+      <c r="E326" t="n">
+        <v>646564</v>
+      </c>
+      <c r="F326" t="n">
+        <v>286372</v>
+      </c>
+      <c r="G326" t="n">
+        <v>44.29</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>253.4</v>
+      </c>
+      <c r="C327" t="n">
+        <v>253.4</v>
+      </c>
+      <c r="D327" t="n">
+        <v>253.4</v>
+      </c>
+      <c r="E327" t="n">
+        <v>378526</v>
+      </c>
+      <c r="F327" t="n">
+        <v>170908</v>
+      </c>
+      <c r="G327" t="n">
+        <v>45.15</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>249.75</v>
+      </c>
+      <c r="C328" t="n">
+        <v>249.75</v>
+      </c>
+      <c r="D328" t="n">
+        <v>249.75</v>
+      </c>
+      <c r="E328" t="n">
+        <v>384424</v>
+      </c>
+      <c r="F328" t="n">
+        <v>172951</v>
+      </c>
+      <c r="G328" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>254.6</v>
+      </c>
+      <c r="C329" t="n">
+        <v>254.6</v>
+      </c>
+      <c r="D329" t="n">
+        <v>254.6</v>
+      </c>
+      <c r="E329" t="n">
+        <v>326062</v>
+      </c>
+      <c r="F329" t="n">
+        <v>141094</v>
+      </c>
+      <c r="G329" t="n">
+        <v>43.27</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="C330" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="D330" t="n">
+        <v>260.6</v>
+      </c>
+      <c r="E330" t="n">
+        <v>739293</v>
+      </c>
+      <c r="F330" t="n">
+        <v>327878</v>
+      </c>
+      <c r="G330" t="n">
+        <v>44.35</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="C331" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="D331" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="E331" t="n">
+        <v>529386</v>
+      </c>
+      <c r="F331" t="n">
+        <v>213169</v>
+      </c>
+      <c r="G331" t="n">
+        <v>40.27</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>247.85</v>
+      </c>
+      <c r="C332" t="n">
+        <v>247.85</v>
+      </c>
+      <c r="D332" t="n">
+        <v>247.85</v>
+      </c>
+      <c r="E332" t="n">
+        <v>340778</v>
+      </c>
+      <c r="F332" t="n">
+        <v>165641</v>
+      </c>
+      <c r="G332" t="n">
+        <v>48.61</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>254.8</v>
+      </c>
+      <c r="C333" t="n">
+        <v>254.8</v>
+      </c>
+      <c r="D333" t="n">
+        <v>254.8</v>
+      </c>
+      <c r="E333" t="n">
+        <v>1018743</v>
+      </c>
+      <c r="F333" t="n">
+        <v>275022</v>
+      </c>
+      <c r="G333" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>269.95</v>
+      </c>
+      <c r="C334" t="n">
+        <v>269.95</v>
+      </c>
+      <c r="D334" t="n">
+        <v>269.95</v>
+      </c>
+      <c r="E334" t="n">
+        <v>1123801</v>
+      </c>
+      <c r="F334" t="n">
+        <v>479887</v>
+      </c>
+      <c r="G334" t="n">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="C335" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="D335" t="n">
+        <v>269.5</v>
+      </c>
+      <c r="E335" t="n">
+        <v>1003726</v>
+      </c>
+      <c r="F335" t="n">
+        <v>417336</v>
+      </c>
+      <c r="G335" t="n">
+        <v>41.58</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>265.3</v>
+      </c>
+      <c r="C336" t="n">
+        <v>265.3</v>
+      </c>
+      <c r="D336" t="n">
+        <v>265.3</v>
+      </c>
+      <c r="E336" t="n">
+        <v>705596</v>
+      </c>
+      <c r="F336" t="n">
+        <v>341684</v>
+      </c>
+      <c r="G336" t="n">
+        <v>48.42</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>259.55</v>
+      </c>
+      <c r="C337" t="n">
+        <v>259.55</v>
+      </c>
+      <c r="D337" t="n">
+        <v>259.55</v>
+      </c>
+      <c r="E337" t="n">
+        <v>450813</v>
+      </c>
+      <c r="F337" t="n">
+        <v>197827</v>
+      </c>
+      <c r="G337" t="n">
+        <v>43.88</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>266</v>
+      </c>
+      <c r="C338" t="n">
+        <v>266</v>
+      </c>
+      <c r="D338" t="n">
+        <v>266</v>
+      </c>
+      <c r="E338" t="n">
+        <v>551731</v>
+      </c>
+      <c r="F338" t="n">
+        <v>260917</v>
+      </c>
+      <c r="G338" t="n">
+        <v>47.29</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>287.75</v>
+      </c>
+      <c r="C339" t="n">
+        <v>287.75</v>
+      </c>
+      <c r="D339" t="n">
+        <v>287.75</v>
+      </c>
+      <c r="E339" t="n">
+        <v>1548816</v>
+      </c>
+      <c r="F339" t="n">
+        <v>923218</v>
+      </c>
+      <c r="G339" t="n">
+        <v>59.61</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="C340" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="D340" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="E340" t="n">
+        <v>3136932</v>
+      </c>
+      <c r="F340" t="n">
+        <v>1286085</v>
+      </c>
+      <c r="G340" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="C341" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="D341" t="n">
+        <v>305.5</v>
+      </c>
+      <c r="E341" t="n">
+        <v>1503289</v>
+      </c>
+      <c r="F341" t="n">
+        <v>661881</v>
+      </c>
+      <c r="G341" t="n">
+        <v>44.03</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>321.85</v>
+      </c>
+      <c r="C342" t="n">
+        <v>321.85</v>
+      </c>
+      <c r="D342" t="n">
+        <v>321.85</v>
+      </c>
+      <c r="E342" t="n">
+        <v>2276706</v>
+      </c>
+      <c r="F342" t="n">
+        <v>1189120</v>
+      </c>
+      <c r="G342" t="n">
+        <v>52.23</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>336.9</v>
+      </c>
+      <c r="C343" t="n">
+        <v>336.9</v>
+      </c>
+      <c r="D343" t="n">
+        <v>336.9</v>
+      </c>
+      <c r="E343" t="n">
+        <v>3869094</v>
+      </c>
+      <c r="F343" t="n">
+        <v>1596361</v>
+      </c>
+      <c r="G343" t="n">
+        <v>41.26</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="B192" t="n">
+      <c r="B344" t="n">
         <v>355.15</v>
       </c>
-      <c r="C192" t="n">
+      <c r="C344" t="n">
+        <v>355.15</v>
+      </c>
+      <c r="D344" t="n">
+        <v>355.15</v>
+      </c>
+      <c r="E344" t="n">
         <v>1867460</v>
       </c>
-      <c r="D192" t="n">
+      <c r="F344" t="n">
         <v>723359</v>
       </c>
-      <c r="E192" t="n">
+      <c r="G344" t="n">
         <v>38.73</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="C345" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="D345" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="E345" t="n">
+        <v>1375942</v>
+      </c>
+      <c r="F345" t="n">
+        <v>681768</v>
+      </c>
+      <c r="G345" t="n">
+        <v>49.55</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>347</v>
+      </c>
+      <c r="C346" t="n">
+        <v>347</v>
+      </c>
+      <c r="D346" t="n">
+        <v>347</v>
+      </c>
+      <c r="E346" t="n">
+        <v>870386</v>
+      </c>
+      <c r="F346" t="n">
+        <v>460976</v>
+      </c>
+      <c r="G346" t="n">
+        <v>52.96</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="C347" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="D347" t="n">
+        <v>371.2</v>
+      </c>
+      <c r="E347" t="n">
+        <v>1561386</v>
+      </c>
+      <c r="F347" t="n">
+        <v>668094</v>
+      </c>
+      <c r="G347" t="n">
+        <v>42.79</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>370.7</v>
+      </c>
+      <c r="C348" t="n">
+        <v>370.7</v>
+      </c>
+      <c r="D348" t="n">
+        <v>370.7</v>
+      </c>
+      <c r="E348" t="n">
+        <v>1686077</v>
+      </c>
+      <c r="F348" t="n">
+        <v>650599</v>
+      </c>
+      <c r="G348" t="n">
+        <v>38.59</v>
       </c>
     </row>
   </sheetData>
